--- a/files/PingPongThread API Reference1.xlsx
+++ b/files/PingPongThread API Reference1.xlsx
@@ -5,16 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\source\pingpong\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCED15F-0135-426C-920C-1F1BE56CD3DC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA04468A-AD49-4C64-9E31-A4A38FFCFF24}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PingPongThread" sheetId="1" r:id="rId1"/>
     <sheet name="MotorOperation" sheetId="4" r:id="rId2"/>
+    <sheet name="ContinuousMotorOperation" sheetId="5" r:id="rId3"/>
+    <sheet name="SingleStepsMotorOperation" sheetId="6" r:id="rId4"/>
+    <sheet name="ScheduledStepsMotorOperation" sheetId="7" r:id="rId5"/>
+    <sheet name="ScheduledPointsMotorOperation" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,8 +35,99 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{64451701-E08B-485E-BACC-344275C0727F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+discovery_group</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> None</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>이면</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 0xFF</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>임</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="89">
   <si>
     <t>Parameters</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -511,6 +606,464 @@
         <scheme val="minor"/>
       </rPr>
       <t>cube_ID=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: int or str
+큐브 ID (1 to 8). "all"이면 모든 cube ID.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discovery_group=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: int or None
+작동시킬 큐브의 소속 그룹 ID (1 to 8). None이면 그룹을 정하지 않음.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>group_mode=False</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: bool
+그룹 모드 설정. True면 그룹 모드, False면 그룹 모드 아님.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discovery_group="all"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or str</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+연결을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 해제할 마스터 로봇이 소속된 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>그룹 ID (1 to 8). "all"이면 연결된 모든 그룹의 마스터 로봇과 연결을 해제한다.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RPM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int
+RPM 단위의 스테퍼 모터 속도. 범위는 -30&lt;=RPM&lt;=-3, RPM=0, 3&lt;=RPM&lt;=30.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int
+SPS 단위의 스테퍼 모터 속도. 범위는 -1000&lt;=SPS&lt;=-100, SPS=0, 100&lt;=SPS&lt;=1000.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cube_ID_list</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or str
+작동시킬 모터의 큐브 ID (1 to 8). "all"이면 모든 cube ID.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>step_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+스테퍼 모터를 돌릴 스텝, 또는 스텝의 스케줄. 단위가 바퀴(cycle)이면 범위는 0&lt;=step&lt;=32.7675이다. 단위가 스텝(STEP)이면 범위는 0&lt;=step&lt;=65535이다. sleep 모드이고 단위가 바퀴(CYCLE)이면 step 초(sec)만큼 쉬고, 범위는 0&lt;=step&lt;=65.535이다. sleep 모드이고 단위가 스텝(STEP)이면 step 밀리초(ms)만큼 쉬고, 범위는 0&lt;=step&lt;=65535이다. 디폴트(None)로 전달되면 단위가 바퀴(CYCLE)이면 1, 단위가 스텝(STEP)이면 2000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 스텝이 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 스텝으로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>speed_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+스테퍼 모터를 돌릴 속도, 또는 속도의 스케줄. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. continue 모드에서 0이면 모터가 멈추고, step, schudule 모드에서 0이면 sleep 모드가 된다. 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 속도로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pause_list=False</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: list or bool
+pause 모드 설정 리스트. True이면 명령이 정지 상태 전달되고, False이면 명령이 바로 재생된다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discovery_group=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:
+작동시킬 큐브의 소속 그룹 ID (1 to 8). None이면 그룹을 정하지 않음.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discovery_group=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: int or None
+스테이터스를 얻을 그룹 ID (1 to 8). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>None이면 그룹을 정하지 않음.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discovery_group=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or None
+연결을 기다릴 그룹 ID (1 to 8). None이면 그룹을 정하지 않음.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discovery_group=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or None
+연결과 관련된 그룹 ID (1 to 8). None이면 그룹을 정하지 않음.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">return </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-&gt; None</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cube_ID</t>
     </r>
     <r>
       <rPr>
@@ -534,6 +1087,78 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
+      <t>speed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: int or float or list or tuple
+스테퍼 모터를 돌릴 속도, 또는 속도의 스케줄. 단위는 RPM이고, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. continue 모드에서 0이면 모터가 멈추고, step, schudule 모드에서 0이면 sleep 모드가 된다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>step_cycle=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: int or float or list or tuple or None
+스테퍼 모터를 돌릴 스텝, 또는 스텝의 스케줄. 단위는 바퀴(cycle). sleep 모드에서는 step_cycle 초(sec)만큼 쉰다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pause=False</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: bool
+pause 모드 설정. True이면 명령이 정지 상태 전달되고, False이면 명령이 바로 재생된다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>discovery_group=None</t>
     </r>
     <r>
@@ -558,7 +1183,117 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>group_mode=False</t>
+      <t>option="continue"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: str
+모드 설정. "continue"이면 continue 모드, "step"이면 step 모드, "schedule"이면 schedule 모드. continue 모드에서는 speed가 int or float 값을 받고, step 모드에서는 speed, step_cycle이 int or float 값을 받고, schedule 모드에서는 speed, step_cycle이 int or float의 list or tuple 값을 받는다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>run_option="continue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": str
+모드 설정. "continue"이면 continue 모드, "step"이면 step 모드, "schedule"이면 schedule 모드이다. continue 모드에서는 speed_list가 int or float의 list or tuple 값을 받고, step 모드에서는 speed_list, step_list가 int or float의 list or tuple 값을 받고, schedule 모드에서는 speed_list, step_list가 int or float의 list or tuple of list or tuple 값을 받는다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>speed_option="RPM"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: str
+speed_list의 단위 설정. "RPM" 또는 "SPS".</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>step_option="CYCLE"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: str
+step_lisit의 단위 설정. "CYCLE" 또는 "STEP".</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Example</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sync=False</t>
     </r>
     <r>
       <rPr>
@@ -569,332 +1304,56 @@
         <scheme val="minor"/>
       </rPr>
       <t>: bool
-그룹 모드 설정. True면 그룹 모드, False면 그룹 모드 아님.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>cube_ID=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: int or str
-큐브 ID (1 to 8). "all"이면 모든 cube ID.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>discovery_group=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: int or None
-작동시킬 큐브의 소속 그룹 ID (1 to 8). None이면 그룹을 정하지 않음.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>group_mode=False</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: bool
-그룹 모드 설정. True면 그룹 모드, False면 그룹 모드 아님.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>discovery_group="all"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: int or str</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-연결을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 해제할 마스터 로봇이 소속된 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>그룹 ID (1 to 8). "all"이면 연결된 모든 그룹의 마스터 로봇과 연결을 해제한다.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>discovery_group=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: int or None
-스테이터스를 얻을 그룹 ID (1 to 8).</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>discovery_group=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: int or None
-연결을 기다릴 그룹 ID (1 to 8).</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>discovery_group=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: int or None
-연결과 관련된 그룹 ID (1 to 8).</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RPM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: float or int
-RPM 단위의 스테퍼 모터 속도. 범위는 -30&lt;=RPM&lt;=-3, RPM=0, 3&lt;=RPM&lt;=30.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SPS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: int
-SPS 단위의 스테퍼 모터 속도. 범위는 -1000&lt;=SPS&lt;=-100, SPS=0, 100&lt;=SPS&lt;=1000.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>cube_ID</t>
+synchronize를 체크할 지 설정. True로 설정하면 step 또는 schedule 모드에서 각 큐브의 한 스텝마다 작동 시간이 동일한지 체크하고, 동일하지 않으면 에러를 발생한다. 소수점 오차가 누적되면 자동으로 리스트를 고쳐준다. False로 설정하면 synchronize를 체크하지 않는다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>time_option=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: str or None
+시간 옵션 설정. None이면 time_list를 받지 않고, speed_list와 step_list를 받아 스테퍼 모터를 작동시킨다. "step"이면 step_list와 time_list를 받아 작동시키며, "speed"이면 speed_list와 time_list를 받아 작동시킨다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stop_motor()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테퍼 모터를 정지시킨다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cube_ID_list="all"</t>
     </r>
     <r>
       <rPr>
@@ -918,18 +1377,44 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>speed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: int or float or list or tuple
-스테퍼 모터를 돌릴 속도, 또는 속도의 스케줄. 단위는 RPM이고, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. continue 모드에서 0이면 모터가 멈추고, step, schudule 모드에서 0이면 sleep 모드가 된다.
+      <t>discovery_group=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or None
+정지시킬 큐브의 소속 그룹 ID (1 to 8). None이면 그룹을 정하지 않음.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cube_ID=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: int or str
+일시정지시킬 모터의 큐브 ID (1 to 8). "all"이면 모든 cube ID.
 </t>
     </r>
     <r>
@@ -942,18 +1427,18 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>step_cycle=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: int or float or list or tuple or None
-스테퍼 모터를 돌릴 스텝, 또는 스텝의 스케줄. 단위는 바퀴(cycle). sleep 모드에서는 step_cycle 초(sec)만큼 쉰다.
+      <t>discovery_group=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: int or None
+일시정지시킬 큐브의 소속 그룹 ID (1 to 8). None이면 그룹을 정하지 않음.
 </t>
     </r>
     <r>
@@ -966,105 +1451,110 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>pause=False</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: bool
-pause 모드 설정. True이면 명령이 정지 상태 전달되고, False이면 명령이 바로 재생된다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>discovery_group=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: int or None
-작동시킬 큐브의 소속 그룹 ID (1 to 8). None이면 그룹을 정하지 않음.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>option="continue"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: str
-모드 설정. "continue"이면 continue 모드, "step"이면 step 모드, "schedule"이면 schedule 모드.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>cube_ID_list</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: int or str
-작동시킬 모터의 큐브 ID (1 to 8). "all"이면 모든 cube ID.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
+      <t>group_mode=False</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: bool
+그룹 모드 설정. True면 그룹 모드, False면 그룹 모드 아님.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>speed_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+스테퍼 모터를 돌릴 속도. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 속도로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>run_motor_continue()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wait=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or float
+기다리는 시간 설정. int or float이면 그 숫자만큼 기다린다. 단위는 초(sec)이다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테퍼 모터를 1개 이상으로 동시에 작동시킨다.  continue 모드는 스테퍼 모터가 계속 돌아가는 모드이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>run_motor_step()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>speed_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+스테퍼 모터를 돌릴 속도. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. 0이면 sleep 모드가 된다. 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 속도로 작동한다.</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1091,8 +1581,144 @@
         <scheme val="minor"/>
       </rPr>
       <t>: float or int or list or tuple or None
-스테퍼 모터를 돌릴 스텝, 또는 스텝의 스케줄. 단위가 바퀴(cycle)이면 범위는 0&lt;=step&lt;=32.7675이다. 단위가 스텝(STEP)이면 범위는 0&lt;=step&lt;=65535이다. sleep 모드이고 단위가 바퀴(CYCLE)이면 step 초(sec)만큼 쉬고, 범위는 0&lt;=step&lt;=65.535이다. sleep 모드이고 단위가 스텝(STEP)이면 step 밀리초(ms)만큼 쉬고, 범위는 0&lt;=step&lt;=65535이다. 디폴트(None)로 전달되면 단위가 바퀴(CYCLE)이면 1, 단위가 스텝(STEP)이면 2000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 스텝이 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 스텝으로 작동한다.</t>
-    </r>
+스테퍼 모터를 돌릴 스텝. 단위가 바퀴(cycle)이면 범위는 0&lt;=step&lt;=32.7675이다. 단위가 스텝(STEP)이면 범위는 0&lt;=step&lt;=65535이다. sleep 모드이고 단위가 바퀴(CYCLE)이면 step 초(sec)만큼 쉬고, 범위는 0&lt;=step&lt;=65.535이다. sleep 모드이고 단위가 스텝(STEP)이면 step 밀리초(ms)만큼 쉬고, 범위는 0&lt;=step&lt;=65535이다. 디폴트(None)로 전달되면 단위가 바퀴(CYCLE)이면 1, 단위가 스텝(STEP)이면 2000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 스텝이 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 스텝으로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>time_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+time_option을 "step" 또는 "speed"로 잡았을 때, 스테퍼 모터를 돌릴 시간, 또는 시간의 스케줄. 단위는 초(sec)이다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>time_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+time_option을 "step" 또는 "speed"로 잡았을 때, 스테퍼 모터를 돌릴 시간. 단위는 초(sec)이다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sync=False</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: bool
+synchronize를 체크할 지 설정. True로 설정하면 각 큐브의 작동 시간이 동일한지 체크하고, 동일하지 않으면 에러를 발생한다. False로 설정하면 synchronize를 체크하지 않는다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wait=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or float or str
+기다리는 시간 설정. int or float이면 그 숫자만큼 기다린다. 단위는 초(sec)이다. "step"이면 가장 오래 작동하는 스테퍼 모터의 작동 시간만큼 기다린다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wait=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or float or str
+기다리는 시간 설정. int or float이면 그 숫자만큼 기다린다. 단위는 초(sec)이다. "step" 또는 "schedule"이면 가장 오래 작동하는 스테퍼 모터의 작동 시간만큼 기다린다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테퍼 모터를 1개 이상으로 동시에 작동시킨다.  step 모드는 특정한 스텝만큼만 모터가 돌아가는 모드이다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1118,43 +1744,129 @@
         <scheme val="minor"/>
       </rPr>
       <t>: float or int or list or tuple or None
-스테퍼 모터를 돌릴 속도, 또는 속도의 스케줄. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. continue 모드에서 0이면 모터가 멈추고, step, schudule 모드에서 0이면 sleep 모드가 된다. 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 속도로 작동한다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pause_list=False</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: list or bool
-pause 모드 설정 리스트. True이면 명령이 정지 상태 전달되고, False이면 명령이 바로 재생된다.
-time_list=None, 
-discovery_group=None, 
-run_option="continue", 
-speed_option="RPM", 
-step_option="CYCLE", 
-sync=False, 
-time_option=None,
-wait=0</t>
-    </r>
+스테퍼 모터를 돌릴 속도의 스케줄. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. continue 모드에서 0이면 모터가 멈추고, step, schudule 모드에서 0이면 sleep 모드가 된다. 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 속도로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>step_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+스테퍼 모터를 돌릴 스텝의 스케줄. 단위가 바퀴(cycle)이면 범위는 0&lt;=step&lt;=32.7675이다. 단위가 스텝(STEP)이면 범위는 0&lt;=step&lt;=65535이다. sleep 모드이고 단위가 바퀴(CYCLE)이면 step 초(sec)만큼 쉬고, 범위는 0&lt;=step&lt;=65.535이다. sleep 모드이고 단위가 스텝(STEP)이면 step 밀리초(ms)만큼 쉬고, 범위는 0&lt;=step&lt;=65535이다. 디폴트(None)로 전달되면 단위가 바퀴(CYCLE)이면 1, 단위가 스텝(STEP)이면 2000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 스텝이 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 스텝으로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>run_motor_schedule()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sync=False</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: bool
+synchronize를 체크할 지 설정. True로 설정하면 각 큐브의 한 스텝마다 작동 시간이 동일한지 체크하고, 동일하지 않으면 에러를 발생한다. 소수점 오차가 누적되면 자동으로 리스트를 고쳐준다. False로 설정하면 synchronize를 체크하지 않는다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wait=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or float or str
+기다리는 시간 설정. int or float이면 그 숫자만큼 기다린다. 단위는 초(sec)이다. "schedule"이면 가장 오래 작동하는 스테퍼 모터의 작동 시간만큼 기다린다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>set_motor_schedule()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cube_ID_list, speed_list, step_list, pause_list=True, time_list=None, discovery_group=None, speed_option="RPM", step_option="CYCLE", sync=False, time_option=None, wait=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+run_motor_schedule() 함수와 완전히 동일하며, pause_list의 디폴트 값만 True이다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇에 스테퍼 모터 스케줄을 설정한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>play_motor_schedule()</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1162,7 +1874,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1239,6 +1951,26 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1254,7 +1986,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1277,11 +2009,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1297,9 +2038,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1325,11 +2063,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1610,117 +2381,120 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="44.625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="68.25" customWidth="1"/>
-    <col min="3" max="3" width="48.625" customWidth="1"/>
-    <col min="4" max="4" width="46.375" customWidth="1"/>
-    <col min="5" max="7" width="12.75" customWidth="1"/>
-    <col min="8" max="10" width="15.25" style="5" customWidth="1"/>
+    <col min="1" max="1" width="44.59765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="68.19921875" customWidth="1"/>
+    <col min="3" max="3" width="48.59765625" customWidth="1"/>
+    <col min="4" max="4" width="46.3984375" customWidth="1"/>
+    <col min="5" max="5" width="48.69921875" customWidth="1"/>
+    <col min="6" max="7" width="12.69921875" customWidth="1"/>
+    <col min="8" max="10" width="15.19921875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="31.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.65">
+      <c r="A1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1"/>
+      <c r="E1" s="10" t="s">
+        <v>60</v>
+      </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-    </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="B4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="B8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -1730,14 +2504,14 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" s="1" customFormat="1" ht="97.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>22</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -1747,14 +2521,14 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="B10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -1764,14 +2538,14 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="B11" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -1781,14 +2555,14 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -1799,163 +2573,984 @@
       <c r="J12" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6F488EC-24D6-45B5-8568-88E8DFA8ADFD}">
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="44.59765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="69.8984375" customWidth="1"/>
+    <col min="3" max="3" width="48.59765625" customWidth="1"/>
+    <col min="4" max="4" width="46.3984375" customWidth="1"/>
+    <col min="5" max="5" width="58" customWidth="1"/>
+    <col min="6" max="7" width="12.69921875" customWidth="1"/>
+    <col min="8" max="10" width="15.19921875" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.65">
+      <c r="A1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="327" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="109.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="107.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="20"/>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="141" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="21"/>
+      <c r="B6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="20"/>
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="21"/>
+      <c r="B7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="20"/>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="21"/>
+      <c r="B8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="20"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="55.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="21"/>
+      <c r="B9" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="20"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="21"/>
+      <c r="B10" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="20"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="109.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="21"/>
+      <c r="B11" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="20"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="21"/>
+      <c r="B12" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="20"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A13" s="21"/>
+      <c r="B13" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="83.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="21"/>
+      <c r="B14" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="73.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="21"/>
+      <c r="B15" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="67.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="21"/>
+      <c r="B16" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="20"/>
+    </row>
+    <row r="17" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.4"/>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="E5:E16"/>
+    <mergeCell ref="A5:A16"/>
+    <mergeCell ref="C5:C16"/>
+    <mergeCell ref="D5:D16"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6F488EC-24D6-45B5-8568-88E8DFA8ADFD}">
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9676A405-038C-4BA5-AF21-824CB7AB106B}">
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="44.625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="69.875" customWidth="1"/>
-    <col min="3" max="3" width="48.625" customWidth="1"/>
-    <col min="4" max="4" width="46.375" customWidth="1"/>
-    <col min="5" max="7" width="12.75" customWidth="1"/>
-    <col min="8" max="10" width="15.25" style="5" customWidth="1"/>
+    <col min="1" max="1" width="44.59765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="69.8984375" customWidth="1"/>
+    <col min="3" max="3" width="48.59765625" customWidth="1"/>
+    <col min="4" max="4" width="46.3984375" customWidth="1"/>
+    <col min="5" max="5" width="58" customWidth="1"/>
+    <col min="6" max="7" width="12.69921875" customWidth="1"/>
+    <col min="8" max="10" width="15.19921875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="31.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.65">
+      <c r="A1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1"/>
+      <c r="E1" s="10" t="s">
+        <v>60</v>
+      </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-    </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="291.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="8" t="s">
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="110.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="21"/>
+      <c r="B3" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="19"/>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="21"/>
+      <c r="B4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="19"/>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="21"/>
+      <c r="B5" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="107.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15"/>
-      <c r="B6" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="16"/>
-    </row>
-    <row r="7" spans="1:10" s="1" customFormat="1" ht="147.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15"/>
-      <c r="B7" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="16"/>
-    </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="210" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15"/>
-      <c r="B8" s="8" t="s">
-        <v>55</v>
-      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="20"/>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="21"/>
+      <c r="B6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="20"/>
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="21"/>
+      <c r="B7" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="20"/>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="136.19999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="16"/>
       <c r="C8" s="6"/>
-      <c r="D8" s="16"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="20"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" s="1" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15"/>
-      <c r="B9" s="8"/>
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="55.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="16"/>
       <c r="C9" s="6"/>
-      <c r="D9" s="16"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="20"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" s="1" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15"/>
-      <c r="B10" s="8"/>
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="16"/>
+      <c r="B10" s="15"/>
       <c r="C10" s="6"/>
-      <c r="D10" s="16"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="20"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="109.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="16"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="20"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="7"/>
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="16"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="20"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
+    <row r="13" spans="1:10" ht="19.2" x14ac:dyDescent="0.4">
+      <c r="A13" s="16"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="83.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="73.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="E16" s="20"/>
+    </row>
+    <row r="17" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="3"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="22"/>
+    </row>
+    <row r="18" spans="1:4" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A5:A10"/>
-    <mergeCell ref="C5:C10"/>
-    <mergeCell ref="D5:D10"/>
+  <mergeCells count="4">
+    <mergeCell ref="E5:E16"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="C2:C7"/>
+    <mergeCell ref="D2:D7"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{456CB50E-7EFD-4EF4-8117-80D93E52D2D4}">
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="44.59765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="69.8984375" customWidth="1"/>
+    <col min="3" max="3" width="48.59765625" customWidth="1"/>
+    <col min="4" max="4" width="46.3984375" customWidth="1"/>
+    <col min="5" max="5" width="58" customWidth="1"/>
+    <col min="6" max="7" width="12.69921875" customWidth="1"/>
+    <col min="8" max="10" width="15.19921875" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.65">
+      <c r="A1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="109.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="21"/>
+      <c r="B3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="19"/>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="140.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="21"/>
+      <c r="B4" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="19"/>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="21"/>
+      <c r="B5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="20"/>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="21"/>
+      <c r="B6" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="20"/>
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="21"/>
+      <c r="B7" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="20"/>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="21"/>
+      <c r="B8" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="20"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="21"/>
+      <c r="B9" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="20"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="73.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="21"/>
+      <c r="B10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="20"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="76.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="21"/>
+      <c r="B11" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="20"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="21"/>
+      <c r="B12" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="20"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A13" s="21"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="83.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="73.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="E16" s="20"/>
+    </row>
+    <row r="17" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="3"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="22"/>
+    </row>
+    <row r="18" spans="1:4" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.4"/>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="E5:E16"/>
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="C2:C13"/>
+    <mergeCell ref="D2:D13"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE5DD678-B88A-4F0A-86B2-9D7B144F70E4}">
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="44.59765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="69.8984375" customWidth="1"/>
+    <col min="3" max="3" width="48.59765625" customWidth="1"/>
+    <col min="4" max="4" width="46.3984375" customWidth="1"/>
+    <col min="5" max="5" width="58" customWidth="1"/>
+    <col min="6" max="7" width="12.69921875" customWidth="1"/>
+    <col min="8" max="10" width="15.19921875" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.65">
+      <c r="A1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="124.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="21"/>
+      <c r="B3" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="19"/>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="159.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="21"/>
+      <c r="B4" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="19"/>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="21"/>
+      <c r="B5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="20"/>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="21"/>
+      <c r="B6" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="20"/>
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="21"/>
+      <c r="B7" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="20"/>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="21"/>
+      <c r="B8" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="20"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="21"/>
+      <c r="B9" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="20"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="70.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="21"/>
+      <c r="B10" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="20"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="21"/>
+      <c r="B11" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="20"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="21"/>
+      <c r="B12" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="20"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A13" s="21"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="87.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="73.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C15" s="1"/>
+      <c r="E15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="E16" s="20"/>
+    </row>
+    <row r="17" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="3"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="22"/>
+    </row>
+    <row r="18" spans="1:4" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.4"/>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="E5:E16"/>
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="C2:C13"/>
+    <mergeCell ref="D2:D13"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5059C841-CB76-442B-BBDC-6E22D445F99C}">
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="44.59765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="69.8984375" customWidth="1"/>
+    <col min="3" max="3" width="48.59765625" customWidth="1"/>
+    <col min="4" max="4" width="46.3984375" customWidth="1"/>
+    <col min="5" max="5" width="58" customWidth="1"/>
+    <col min="6" max="7" width="12.69921875" customWidth="1"/>
+    <col min="8" max="10" width="15.19921875" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.65">
+      <c r="A1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="109.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="21"/>
+      <c r="B3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="19"/>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="140.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="21"/>
+      <c r="B4" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="19"/>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="21"/>
+      <c r="B5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="20"/>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="21"/>
+      <c r="B6" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="20"/>
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="21"/>
+      <c r="B7" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="20"/>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="21"/>
+      <c r="B8" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="20"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="21"/>
+      <c r="B9" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="20"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="73.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="21"/>
+      <c r="B10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="20"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="76.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="21"/>
+      <c r="B11" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="20"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="21"/>
+      <c r="B12" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="20"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A13" s="21"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="83.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="73.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="E16" s="20"/>
+    </row>
+    <row r="17" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="3"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="22"/>
+    </row>
+    <row r="18" spans="1:4" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.4"/>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="C2:C13"/>
+    <mergeCell ref="D2:D13"/>
+    <mergeCell ref="E5:E16"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/files/PingPongThread API Reference1.xlsx
+++ b/files/PingPongThread API Reference1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\source\pingpong\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA04468A-AD49-4C64-9E31-A4A38FFCFF24}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892EB145-7FDC-4190-B7D5-16AF210A3985}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="102">
   <si>
     <t>Parameters</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -581,10 +581,6 @@
   </si>
   <si>
     <t>pause 상태인 스테퍼 모터 명령을 다시 재생시키도록 명령을 보낸다. pause 상태가 아니면 다시 재생하지 않는다.</t>
-  </si>
-  <si>
-    <t>run_motor()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>로봇 1개에 대한 스테퍼 모터를 작동시킨다. continue 모드, step 모드, schedule 모드를 담당한다. continue 모드는 스테퍼 모터가 계속 돌아가는 모드, step 모드는 특정한 스텝만큼만 모터가 돌아가는 모드, schedule 모드는 특정한 스케줄의 속도, 스텝을 가지고 스케줄 만큼 돌아가는 모드이다.</t>
@@ -840,60 +836,6 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>step_list=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: float or int or list or tuple or None
-스테퍼 모터를 돌릴 스텝, 또는 스텝의 스케줄. 단위가 바퀴(cycle)이면 범위는 0&lt;=step&lt;=32.7675이다. 단위가 스텝(STEP)이면 범위는 0&lt;=step&lt;=65535이다. sleep 모드이고 단위가 바퀴(CYCLE)이면 step 초(sec)만큼 쉬고, 범위는 0&lt;=step&lt;=65.535이다. sleep 모드이고 단위가 스텝(STEP)이면 step 밀리초(ms)만큼 쉬고, 범위는 0&lt;=step&lt;=65535이다. 디폴트(None)로 전달되면 단위가 바퀴(CYCLE)이면 1, 단위가 스텝(STEP)이면 2000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 스텝이 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 스텝으로 작동한다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>speed_list=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: float or int or list or tuple or None
-스테퍼 모터를 돌릴 속도, 또는 속도의 스케줄. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. continue 모드에서 0이면 모터가 멈추고, step, schudule 모드에서 0이면 sleep 모드가 된다. 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 속도로 작동한다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>pause_list=False</t>
     </r>
     <r>
@@ -1063,7 +1005,147 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>cube_ID</t>
+      <t>run_option="continue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>": str
+모드 설정. "continue"이면 continue 모드, "step"이면 step 모드, "schedule"이면 schedule 모드이다. continue 모드에서는 speed_list가 int or float의 list or tuple 값을 받고, step 모드에서는 speed_list, step_list가 int or float의 list or tuple 값을 받고, schedule 모드에서는 speed_list, step_list가 int or float의 list or tuple of list or tuple 값을 받는다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>speed_option="RPM"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: str
+speed_list의 단위 설정. "RPM" 또는 "SPS".</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>step_option="CYCLE"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: str
+step_lisit의 단위 설정. "CYCLE" 또는 "STEP".</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Example</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sync=False</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: bool
+synchronize를 체크할 지 설정. True로 설정하면 step 또는 schedule 모드에서 각 큐브의 한 스텝마다 작동 시간이 동일한지 체크하고, 동일하지 않으면 에러를 발생한다. 소수점 오차가 누적되면 자동으로 리스트를 고쳐준다. False로 설정하면 synchronize를 체크하지 않는다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>time_option=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: str or None
+시간 옵션 설정. None이면 time_list를 받지 않고, speed_list와 step_list를 받아 스테퍼 모터를 작동시킨다. "step"이면 step_list와 time_list를 받아 작동시키며, "speed"이면 speed_list와 time_list를 받아 작동시킨다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테퍼 모터를 정지시킨다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cube_ID_list="all"</t>
     </r>
     <r>
       <rPr>
@@ -1087,6 +1169,457 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
+      <t>discovery_group=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or None
+정지시킬 큐브의 소속 그룹 ID (1 to 8). None이면 그룹을 정하지 않음.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cube_ID=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: int or str
+일시정지시킬 모터의 큐브 ID (1 to 8). "all"이면 모든 cube ID.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discovery_group=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: int or None
+일시정지시킬 큐브의 소속 그룹 ID (1 to 8). None이면 그룹을 정하지 않음.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>group_mode=False</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: bool
+그룹 모드 설정. True면 그룹 모드, False면 그룹 모드 아님.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>run_motor_continue()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wait=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or float
+기다리는 시간 설정. int or float이면 그 숫자만큼 기다린다. 단위는 초(sec)이다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테퍼 모터를 1개 이상으로 동시에 작동시킨다.  continue 모드는 스테퍼 모터가 계속 돌아가는 모드이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>run_motor_step()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>time_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+time_option을 "step" 또는 "speed"로 잡았을 때, 스테퍼 모터를 돌릴 시간, 또는 시간의 스케줄. 단위는 초(sec)이다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>time_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+time_option을 "step" 또는 "speed"로 잡았을 때, 스테퍼 모터를 돌릴 시간. 단위는 초(sec)이다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sync=False</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: bool
+synchronize를 체크할 지 설정. True로 설정하면 각 큐브의 작동 시간이 동일한지 체크하고, 동일하지 않으면 에러를 발생한다. False로 설정하면 synchronize를 체크하지 않는다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wait=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or float or str
+기다리는 시간 설정. int or float이면 그 숫자만큼 기다린다. 단위는 초(sec)이다. "step"이면 가장 오래 작동하는 스테퍼 모터의 작동 시간만큼 기다린다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wait=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or float or str
+기다리는 시간 설정. int or float이면 그 숫자만큼 기다린다. 단위는 초(sec)이다. "step" 또는 "schedule"이면 가장 오래 작동하는 스테퍼 모터의 작동 시간만큼 기다린다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테퍼 모터를 1개 이상으로 동시에 작동시킨다.  step 모드는 특정한 스텝만큼만 모터가 돌아가는 모드이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>speed_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+스테퍼 모터를 돌릴 속도의 스케줄. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. continue 모드에서 0이면 모터가 멈추고, step, schudule 모드에서 0이면 sleep 모드가 된다. 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 속도로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>step_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+스테퍼 모터를 돌릴 스텝의 스케줄. 단위가 바퀴(cycle)이면 범위는 0&lt;=step&lt;=32.7675이다. 단위가 스텝(STEP)이면 범위는 0&lt;=step&lt;=65535이다. sleep 모드이고 단위가 바퀴(CYCLE)이면 step 초(sec)만큼 쉬고, 범위는 0&lt;=step&lt;=65.535이다. sleep 모드이고 단위가 스텝(STEP)이면 step 밀리초(ms)만큼 쉬고, 범위는 0&lt;=step&lt;=65535이다. 디폴트(None)로 전달되면 단위가 바퀴(CYCLE)이면 1, 단위가 스텝(STEP)이면 2000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 스텝이 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 스텝으로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>run_motor_schedule()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sync=False</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: bool
+synchronize를 체크할 지 설정. True로 설정하면 각 큐브의 한 스텝마다 작동 시간이 동일한지 체크하고, 동일하지 않으면 에러를 발생한다. 소수점 오차가 누적되면 자동으로 리스트를 고쳐준다. False로 설정하면 synchronize를 체크하지 않는다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wait=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or float or str
+기다리는 시간 설정. int or float이면 그 숫자만큼 기다린다. 단위는 초(sec)이다. "schedule"이면 가장 오래 작동하는 스테퍼 모터의 작동 시간만큼 기다린다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>set_motor_schedule()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cube_ID_list, speed_list, step_list, pause_list=True, time_list=None, discovery_group=None, speed_option="RPM", step_option="CYCLE", sync=False, time_option=None, wait=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+run_motor_schedule() 함수와 완전히 동일하며, pause_list의 디폴트 값만 True이다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇에 스테퍼 모터 스케줄을 설정한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>play_motor_schedule()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cube_ID_list = [1, 3, 4]
+speed_list = [30, -30, 15]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cube_ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: int or str
+작동시킬 모터의 큐브 ID (1 to 8). "all"이면 모든 cube ID.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>speed</t>
     </r>
     <r>
@@ -1098,7 +1631,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">: int or float or list or tuple
-스테퍼 모터를 돌릴 속도, 또는 속도의 스케줄. 단위는 RPM이고, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. continue 모드에서 0이면 모터가 멈추고, step, schudule 모드에서 0이면 sleep 모드가 된다.
+스테퍼 모터를 돌릴 속도, 또는 속도의 스케줄. 단위는 RPM이고, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. continue 모드에서 0이면 모터가 멈추고, step, schudule 모드에서 0이면 sleep 모드가 된다. speed가 양수이면 시계방향, 음수이면 반시계방향으로 회전한다.
 </t>
     </r>
     <r>
@@ -1209,90 +1742,323 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>run_option="continue</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>": str
-모드 설정. "continue"이면 continue 모드, "step"이면 step 모드, "schedule"이면 schedule 모드이다. continue 모드에서는 speed_list가 int or float의 list or tuple 값을 받고, step 모드에서는 speed_list, step_list가 int or float의 list or tuple 값을 받고, schedule 모드에서는 speed_list, step_list가 int or float의 list or tuple of list or tuple 값을 받는다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>speed_option="RPM"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: str
-speed_list의 단위 설정. "RPM" 또는 "SPS".</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>step_option="CYCLE"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: str
-step_lisit의 단위 설정. "CYCLE" 또는 "STEP".</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Example</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
+      <t>speed_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: float or int or list or tuple or None
+스테퍼 모터를 돌릴 속도, 또는 속도의 스케줄. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. continue 모드에서 0이면 모터가 멈추고, step, schudule 모드에서 0이면 sleep 모드가 된다. speed가 양수이면 시계방향, 음수이면 반시계방향으로 회전한다. 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 속도로 작동한다. </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>step_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+스테퍼 모터를 돌릴 스텝, 또는 스텝의 스케줄. 단위가 바퀴(cycle)이면 범위는 -32.7675&lt;=step&lt;=32.7675이다. 단위가 스텝(STEP)이면 범위는 -65535&lt;=step&lt;=65535이다. sleep 모드이고 단위가 바퀴(CYCLE)이면 step 초(sec)만큼 쉬고, 범위는 0&lt;=step&lt;=65.535이다. sleep 모드이고 단위가 스텝(STEP)이면 step 밀리초(ms)만큼 쉬고, 범위는 0&lt;=step&lt;=65535이다. 스텝이 음수이면 speed_list에서 정해진 방향에 반대로 회전한다. 디폴트(None)로 전달되면 단위가 바퀴(CYCLE)이면 1, 단위가 스텝(STEP)이면 2000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 스텝이 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 스텝으로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>speed_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+스테퍼 모터를 돌릴 속도. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. speed가 양수이면 시계방향, 음수이면 반시계방향으로 회전한다 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 속도로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>speed_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+스테퍼 모터를 돌릴 속도. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. 0이면 sleep 모드가 된다. speed가 양수이면 시계방향, 음수이면 반시계방향으로 회전한다. 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 속도로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>step_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+스테퍼 모터를 돌릴 스텝. 단위가 바퀴(cycle)이면 범위는 -32.7675&lt;=step&lt;=32.7675이다. 단위가 스텝(STEP)이면 범위는 -65535&lt;=step&lt;=65535이다. sleep 모드이고 단위가 바퀴(CYCLE)이면 step 초(sec)만큼 쉬고, 범위는 0&lt;=step&lt;=65.535이다. sleep 모드이고 단위가 스텝(STEP)이면 step 밀리초(ms)만큼 쉬고, 범위는 0&lt;=step&lt;=65535이다. 스텝이 음수이면 speed_list에서 정해진 방향에 반대로 회전한다. 디폴트(None)로 전달되면 단위가 바퀴(CYCLE)이면 1, 단위가 스텝(STEP)이면 2000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 스텝이 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 스텝으로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ex1)
+cube_ID_list = [1, 3, 4]
+speed_list = [30, -30, 15]
+step_list = 2
+Ex2)
+cube_ID_list = [1, 3, 4]
+speed_list = 30
+time_list = [1, 2, 3]
+time_option = "speed"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ex1)
+cube_ID_list = [1, 3, 4]
+speed_list = [[30, 15, -15], [-30, 15, -15], [15, 10]]
+step_list = [[1, 2, 1], [2, 2, 1], [-2, 1]]
+Ex2)
+cube_ID_list = [1, 3, 4]
+speed_list = [[30, 15, -15], [-30, 15, -15], [15, 10, 20]]
+time_list = [[1, 2, 3]]
+time_option = "speed"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테퍼 모터를 1개 이상으로 동시에 작동시킨다.  정한 schedule의 특정 부분을 재생시키는 스케줄을 짠다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>repeat_list=[[1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">]: list or tuple
+플레이 시킬 스케줄을 반복하는 횟수의 리스트. </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>start_point_list=[[None]]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: list or tuple
+플레이 시킬 스케줄의 시작 인덱스의 리스트. 디폴트(None)이면 처음 인덱스(0)으로 설정된다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>start_and_stop_list=[[None]]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: list or tuple
+플레이 시킬 스케줄의 처음과 끝의 인덱스의 리스트. 디폴트(None)가 아닌 값이 입력되면, start_point_list와 stop_point_list는 무시된다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>pause_list=False</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: list or bool
+pause 모드 설정 리스트. True이면 명령이 정지 상태 전달되고, False이면 명령이 바로 재생된다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discovery_group=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or None
+작동시킬 큐브의 소속 그룹 ID (1 to 8). None이면 그룹을 정하지 않음.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stop_motor()</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">run_motor()
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(expand에서 보수가 필요한가? 길이가 다른 경우.)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>stop_point_list=[[None]]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: list or tuple
+플레이 시킬 스케줄의 끝 인덱스의 리스트. 디폴트(None)이면 로봇에 지정된 스케줄의 끝의 인덱스로 설정된다. 인덱스를 "end"라고 하면 로봇에 지정한 스케줄의의 끝의 인덱스로 설정된다. 플레이는 이 끝의 인덱스를 포함하여 재생된다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ex1)
+cube_ID_list = [1, 2, 4]
+repeat_list = [[1, 3], [2, 3, 3], [2]]
+start_point_list = [[0, 3], [2, 3, 4], [1]]
+stop_point_list = [[1, 6], [4, 5, 8], [1]]
+해석: 1번 큐브 스케줄 0번부터 1번까지 1번 반복, 3번부터 6번까지 3번 반복
+2번 큐브 스케줄 2번부터 4번까지 2번 반복, 3번부터 5번까지 3번 반복, 4번부터 8번까지 3번 반복
+3번 큐브 스케줄 1번만 2번 반복
+Ex2)
+cube_ID_list = [1, 2, 4]
+repeat_list = [[1, 3], [2, 3, 3], [2]]
+start_and_stop_point_list = [[[0, 1], [3, 6]], [[2, 4], [3, 5], [4, 8]], [[1, 1]]]
+해석: Ex1과 동일.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t>sync=False</t>
     </r>
     <r>
@@ -1300,83 +2066,41 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: bool
-synchronize를 체크할 지 설정. True로 설정하면 step 또는 schedule 모드에서 각 큐브의 한 스텝마다 작동 시간이 동일한지 체크하고, 동일하지 않으면 에러를 발생한다. 소수점 오차가 누적되면 자동으로 리스트를 고쳐준다. False로 설정하면 synchronize를 체크하지 않는다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>time_option=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: str or None
-시간 옵션 설정. None이면 time_list를 받지 않고, speed_list와 step_list를 받아 스테퍼 모터를 작동시킨다. "step"이면 step_list와 time_list를 받아 작동시키며, "speed"이면 speed_list와 time_list를 받아 작동시킨다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stop_motor()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테퍼 모터를 정지시킨다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>cube_ID_list="all"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: int or str
-작동시킬 모터의 큐브 ID (1 to 8). "all"이면 모든 cube ID.
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: bool</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>synchronize를 체크할 지 설정. True로 설정하면 각 큐브가 동일한 인덱스를 작동시키는지 체크한다. False로 설정하면 체크하지 않는다.
+(보수 필요?)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t>discovery_group=None</t>
     </r>
     <r>
@@ -1384,489 +2108,13 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
-        <family val="2"/>
+        <family val="3"/>
+        <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
       <t>: int or None
-정지시킬 큐브의 소속 그룹 ID (1 to 8). None이면 그룹을 정하지 않음.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>cube_ID=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: int or str
-일시정지시킬 모터의 큐브 ID (1 to 8). "all"이면 모든 cube ID.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>discovery_group=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: int or None
-일시정지시킬 큐브의 소속 그룹 ID (1 to 8). None이면 그룹을 정하지 않음.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>group_mode=False</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: bool
-그룹 모드 설정. True면 그룹 모드, False면 그룹 모드 아님.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>speed_list=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: float or int or list or tuple or None
-스테퍼 모터를 돌릴 속도. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 속도로 작동한다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>run_motor_continue()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>wait=0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: int or float
-기다리는 시간 설정. int or float이면 그 숫자만큼 기다린다. 단위는 초(sec)이다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테퍼 모터를 1개 이상으로 동시에 작동시킨다.  continue 모드는 스테퍼 모터가 계속 돌아가는 모드이다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>run_motor_step()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>speed_list=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: float or int or list or tuple or None
-스테퍼 모터를 돌릴 속도. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. 0이면 sleep 모드가 된다. 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 속도로 작동한다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>step_list=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: float or int or list or tuple or None
-스테퍼 모터를 돌릴 스텝. 단위가 바퀴(cycle)이면 범위는 0&lt;=step&lt;=32.7675이다. 단위가 스텝(STEP)이면 범위는 0&lt;=step&lt;=65535이다. sleep 모드이고 단위가 바퀴(CYCLE)이면 step 초(sec)만큼 쉬고, 범위는 0&lt;=step&lt;=65.535이다. sleep 모드이고 단위가 스텝(STEP)이면 step 밀리초(ms)만큼 쉬고, 범위는 0&lt;=step&lt;=65535이다. 디폴트(None)로 전달되면 단위가 바퀴(CYCLE)이면 1, 단위가 스텝(STEP)이면 2000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 스텝이 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 스텝으로 작동한다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>time_list=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: float or int or list or tuple or None
-time_option을 "step" 또는 "speed"로 잡았을 때, 스테퍼 모터를 돌릴 시간, 또는 시간의 스케줄. 단위는 초(sec)이다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>time_list=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: float or int or list or tuple or None
-time_option을 "step" 또는 "speed"로 잡았을 때, 스테퍼 모터를 돌릴 시간. 단위는 초(sec)이다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>sync=False</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: bool
-synchronize를 체크할 지 설정. True로 설정하면 각 큐브의 작동 시간이 동일한지 체크하고, 동일하지 않으면 에러를 발생한다. False로 설정하면 synchronize를 체크하지 않는다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>wait=0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: int or float or str
-기다리는 시간 설정. int or float이면 그 숫자만큼 기다린다. 단위는 초(sec)이다. "step"이면 가장 오래 작동하는 스테퍼 모터의 작동 시간만큼 기다린다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>wait=0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: int or float or str
-기다리는 시간 설정. int or float이면 그 숫자만큼 기다린다. 단위는 초(sec)이다. "step" 또는 "schedule"이면 가장 오래 작동하는 스테퍼 모터의 작동 시간만큼 기다린다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테퍼 모터를 1개 이상으로 동시에 작동시킨다.  step 모드는 특정한 스텝만큼만 모터가 돌아가는 모드이다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>speed_list=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: float or int or list or tuple or None
-스테퍼 모터를 돌릴 속도의 스케줄. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. continue 모드에서 0이면 모터가 멈추고, step, schudule 모드에서 0이면 sleep 모드가 된다. 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 속도로 작동한다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>step_list=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: float or int or list or tuple or None
-스테퍼 모터를 돌릴 스텝의 스케줄. 단위가 바퀴(cycle)이면 범위는 0&lt;=step&lt;=32.7675이다. 단위가 스텝(STEP)이면 범위는 0&lt;=step&lt;=65535이다. sleep 모드이고 단위가 바퀴(CYCLE)이면 step 초(sec)만큼 쉬고, 범위는 0&lt;=step&lt;=65.535이다. sleep 모드이고 단위가 스텝(STEP)이면 step 밀리초(ms)만큼 쉬고, 범위는 0&lt;=step&lt;=65535이다. 디폴트(None)로 전달되면 단위가 바퀴(CYCLE)이면 1, 단위가 스텝(STEP)이면 2000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 스텝이 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 스텝으로 작동한다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>run_motor_schedule()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>sync=False</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: bool
-synchronize를 체크할 지 설정. True로 설정하면 각 큐브의 한 스텝마다 작동 시간이 동일한지 체크하고, 동일하지 않으면 에러를 발생한다. 소수점 오차가 누적되면 자동으로 리스트를 고쳐준다. False로 설정하면 synchronize를 체크하지 않는다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>wait=0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: int or float or str
-기다리는 시간 설정. int or float이면 그 숫자만큼 기다린다. 단위는 초(sec)이다. "schedule"이면 가장 오래 작동하는 스테퍼 모터의 작동 시간만큼 기다린다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>set_motor_schedule()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>cube_ID_list, speed_list, step_list, pause_list=True, time_list=None, discovery_group=None, speed_option="RPM", step_option="CYCLE", sync=False, time_option=None, wait=0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-run_motor_schedule() 함수와 완전히 동일하며, pause_list의 디폴트 값만 True이다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>로봇에 스테퍼 모터 스케줄을 설정한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>play_motor_schedule()</t>
+작동시킬 큐브의 소속 그룹 ID (1 to 8). None이면 그룹을 정하지 않는다.</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1874,7 +2122,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1971,6 +2219,14 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2022,7 +2278,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2064,9 +2320,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2078,8 +2331,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2087,11 +2343,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2100,6 +2356,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2408,7 +2670,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -2442,7 +2704,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>16</v>
@@ -2478,7 +2740,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>17</v>
@@ -2492,7 +2754,7 @@
         <v>19</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>16</v>
@@ -2509,7 +2771,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>22</v>
@@ -2526,7 +2788,7 @@
         <v>24</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>32</v>
@@ -2543,7 +2805,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>33</v>
@@ -2585,7 +2847,7 @@
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.59765625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="69.8984375" customWidth="1"/>
+    <col min="2" max="2" width="104.8984375" customWidth="1"/>
     <col min="3" max="3" width="48.59765625" customWidth="1"/>
     <col min="4" max="4" width="46.3984375" customWidth="1"/>
     <col min="5" max="5" width="58" customWidth="1"/>
@@ -2607,25 +2869,25 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
     </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="327" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="280.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="12" t="s">
         <v>35</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" ht="109.2" customHeight="1" x14ac:dyDescent="0.4">
@@ -2633,7 +2895,7 @@
         <v>36</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>34</v>
@@ -2647,7 +2909,7 @@
         <v>37</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>34</v>
@@ -2658,56 +2920,56 @@
     </row>
     <row r="5" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="21" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>42</v>
+        <v>46</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>41</v>
       </c>
       <c r="E5" s="20"/>
     </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" ht="141" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="102.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="21"/>
       <c r="B6" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="19"/>
+        <v>83</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="20"/>
     </row>
-    <row r="7" spans="1:10" s="1" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="115.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="21"/>
       <c r="B7" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="19"/>
+        <v>84</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="20"/>
     </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="21"/>
       <c r="B8" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="19"/>
+        <v>47</v>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="20"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" s="1" customFormat="1" ht="55.8" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="21"/>
       <c r="B9" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="19"/>
+        <v>66</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="20"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -2716,22 +2978,22 @@
     <row r="10" spans="1:10" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="21"/>
       <c r="B10" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="19"/>
+        <v>48</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="20"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" s="1" customFormat="1" ht="109.8" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="67.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="21"/>
       <c r="B11" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="19"/>
+        <v>53</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="20"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -2740,10 +3002,10 @@
     <row r="12" spans="1:10" s="1" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="21"/>
       <c r="B12" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="19"/>
+        <v>54</v>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="20"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -2751,52 +3013,52 @@
     </row>
     <row r="13" spans="1:10" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A13" s="21"/>
-      <c r="B13" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="19"/>
+      <c r="B13" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="20"/>
     </row>
-    <row r="14" spans="1:10" ht="83.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="21"/>
       <c r="B14" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="19"/>
+        <v>57</v>
+      </c>
+      <c r="C14" s="22"/>
+      <c r="D14" s="23"/>
       <c r="E14" s="20"/>
     </row>
-    <row r="15" spans="1:10" ht="73.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" ht="49.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="21"/>
-      <c r="B15" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="19"/>
+      <c r="B15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="20"/>
     </row>
-    <row r="16" spans="1:10" ht="67.8" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" ht="56.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="21"/>
-      <c r="B16" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="19"/>
+      <c r="B16" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="23"/>
       <c r="E16" s="20"/>
     </row>
     <row r="17" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="22" t="s">
-        <v>64</v>
+      <c r="D17" s="18" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -2818,7 +3080,7 @@
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.59765625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="69.8984375" customWidth="1"/>
+    <col min="2" max="2" width="87.69921875" customWidth="1"/>
     <col min="3" max="3" width="48.59765625" customWidth="1"/>
     <col min="4" max="4" width="46.3984375" customWidth="1"/>
     <col min="5" max="5" width="58" customWidth="1"/>
@@ -2840,7 +3102,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -2849,137 +3111,137 @@
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="24" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" ht="110.4" customHeight="1" x14ac:dyDescent="0.4">
+        <v>64</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="21"/>
       <c r="B3" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="19"/>
-    </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="20"/>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="21"/>
       <c r="B4" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="19"/>
-    </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+        <v>47</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="20"/>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="21"/>
       <c r="B5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="19"/>
+        <v>48</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="20"/>
     </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="21"/>
       <c r="B6" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="19"/>
+        <v>54</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="20"/>
     </row>
     <row r="7" spans="1:10" s="1" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="21"/>
-      <c r="B7" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="19"/>
+      <c r="B7" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="20"/>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="136.19999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="16"/>
+      <c r="A8" s="15"/>
       <c r="C8" s="6"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="20"/>
+      <c r="D8" s="17"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" s="1" customFormat="1" ht="55.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="16"/>
+      <c r="A9" s="15"/>
       <c r="C9" s="6"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="20"/>
+      <c r="D9" s="17"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="16"/>
-      <c r="B10" s="15"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="6"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="20"/>
+      <c r="D10" s="17"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" s="1" customFormat="1" ht="109.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="16"/>
+      <c r="A11" s="15"/>
       <c r="B11" s="7"/>
       <c r="C11" s="6"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="20"/>
+      <c r="D11" s="17"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" s="1" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="16"/>
       <c r="C12" s="6"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="20"/>
+      <c r="D12" s="17"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" ht="19.2" x14ac:dyDescent="0.4">
-      <c r="A13" s="16"/>
+      <c r="A13" s="15"/>
       <c r="C13" s="6"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="20"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:10" ht="83.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="E14" s="20"/>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:10" ht="73.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="E15" s="20"/>
+      <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="E16" s="20"/>
+      <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="22"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="E5:E16"/>
     <mergeCell ref="A2:A7"/>
     <mergeCell ref="C2:C7"/>
     <mergeCell ref="D2:D7"/>
+    <mergeCell ref="E2:E7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2992,8 +3254,8 @@
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.59765625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="69.8984375" customWidth="1"/>
-    <col min="3" max="3" width="48.59765625" customWidth="1"/>
+    <col min="2" max="2" width="115.19921875" customWidth="1"/>
+    <col min="3" max="3" width="28.796875" customWidth="1"/>
     <col min="4" max="4" width="46.3984375" customWidth="1"/>
     <col min="5" max="5" width="58" customWidth="1"/>
     <col min="6" max="7" width="12.69921875" customWidth="1"/>
@@ -3014,7 +3276,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -3023,68 +3285,73 @@
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" ht="109.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E2" s="26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="88.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="21"/>
       <c r="B3" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="19"/>
-    </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="140.4" customHeight="1" x14ac:dyDescent="0.4">
+        <v>86</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="20"/>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="108.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="21"/>
       <c r="B4" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="19"/>
-    </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
+        <v>87</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="20"/>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="21"/>
       <c r="B5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="19"/>
+        <v>47</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="20"/>
     </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="21"/>
       <c r="B6" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="19"/>
+        <v>67</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="20"/>
     </row>
-    <row r="7" spans="1:10" s="1" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="21"/>
       <c r="B7" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="19"/>
+        <v>48</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="20"/>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="21"/>
       <c r="B8" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="19"/>
+        <v>54</v>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="20"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -3093,34 +3360,34 @@
     <row r="9" spans="1:10" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="21"/>
       <c r="B9" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="19"/>
+        <v>55</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="20"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" s="1" customFormat="1" ht="73.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="21"/>
       <c r="B10" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="19"/>
+        <v>68</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="20"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" s="1" customFormat="1" ht="76.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="57.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="21"/>
-      <c r="B11" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="19"/>
+      <c r="B11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="20"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -3128,11 +3395,11 @@
     </row>
     <row r="12" spans="1:10" s="1" customFormat="1" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="21"/>
-      <c r="B12" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="19"/>
+      <c r="B12" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="20"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -3140,32 +3407,32 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="21"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="19"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="20"/>
     </row>
     <row r="14" spans="1:10" ht="83.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="E14" s="20"/>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:10" ht="73.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="E15" s="20"/>
+      <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="E16" s="20"/>
+      <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="22"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="E5:E16"/>
     <mergeCell ref="A2:A13"/>
     <mergeCell ref="C2:C13"/>
     <mergeCell ref="D2:D13"/>
+    <mergeCell ref="E2:E13"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3200,7 +3467,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -3209,68 +3476,73 @@
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="21" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>42</v>
+        <v>46</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" ht="124.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="21"/>
       <c r="B3" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="19"/>
+        <v>72</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="20"/>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="159.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="21"/>
       <c r="B4" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="19"/>
+        <v>73</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="20"/>
     </row>
     <row r="5" spans="1:10" s="1" customFormat="1" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="21"/>
       <c r="B5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="19"/>
+        <v>47</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="20"/>
     </row>
     <row r="6" spans="1:10" s="1" customFormat="1" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="21"/>
       <c r="B6" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="19"/>
+        <v>66</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="20"/>
     </row>
     <row r="7" spans="1:10" s="1" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="21"/>
       <c r="B7" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="19"/>
+        <v>95</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="20"/>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="21"/>
       <c r="B8" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="19"/>
+        <v>54</v>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="20"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -3278,11 +3550,11 @@
     </row>
     <row r="9" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="21"/>
-      <c r="B9" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="19"/>
+      <c r="B9" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="20"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -3291,10 +3563,10 @@
     <row r="10" spans="1:10" s="1" customFormat="1" ht="70.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="21"/>
       <c r="B10" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="19"/>
+        <v>75</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="20"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -3302,11 +3574,11 @@
     </row>
     <row r="11" spans="1:10" s="1" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="21"/>
-      <c r="B11" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="19"/>
+      <c r="B11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="20"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -3314,11 +3586,11 @@
     </row>
     <row r="12" spans="1:10" s="1" customFormat="1" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="21"/>
-      <c r="B12" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="19"/>
+      <c r="B12" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="20"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -3326,45 +3598,45 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="21"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="19"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="20"/>
     </row>
     <row r="14" spans="1:10" ht="87.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E14" s="20"/>
+        <v>79</v>
+      </c>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:10" ht="73.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="1"/>
-      <c r="E15" s="20"/>
+      <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="E16" s="20"/>
+      <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="22"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="E5:E16"/>
     <mergeCell ref="A2:A13"/>
     <mergeCell ref="C2:C13"/>
     <mergeCell ref="D2:D13"/>
+    <mergeCell ref="E2:E13"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3378,9 +3650,9 @@
   <cols>
     <col min="1" max="1" width="44.59765625" style="4" customWidth="1"/>
     <col min="2" max="2" width="69.8984375" customWidth="1"/>
-    <col min="3" max="3" width="48.59765625" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
     <col min="4" max="4" width="46.3984375" customWidth="1"/>
-    <col min="5" max="5" width="58" customWidth="1"/>
+    <col min="5" max="5" width="66.59765625" customWidth="1"/>
     <col min="6" max="7" width="12.69921875" customWidth="1"/>
     <col min="8" max="10" width="15.19921875" style="5" customWidth="1"/>
   </cols>
@@ -3399,7 +3671,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -3407,150 +3679,148 @@
       <c r="J1" s="8"/>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="21" t="s">
-        <v>88</v>
+      <c r="A2" s="24" t="s">
+        <v>80</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" ht="109.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="21"/>
+        <v>46</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="28"/>
       <c r="B3" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="19"/>
-    </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="140.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="21"/>
-      <c r="B4" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="19"/>
-    </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="21"/>
-      <c r="B5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="19"/>
+        <v>91</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="20"/>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="50.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="28"/>
+      <c r="B4" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="20"/>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="70.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="28"/>
+      <c r="B5" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="20"/>
     </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="21"/>
-      <c r="B6" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="19"/>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="28"/>
+      <c r="B6" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="20"/>
     </row>
-    <row r="7" spans="1:10" s="1" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="21"/>
-      <c r="B7" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="19"/>
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="28"/>
+      <c r="B7" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="20"/>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="21"/>
-      <c r="B8" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="19"/>
+      <c r="A8" s="28"/>
+      <c r="B8" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="20"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="21"/>
-      <c r="B9" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="19"/>
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="73.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="28"/>
+      <c r="B9" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="20"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" s="1" customFormat="1" ht="73.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="21"/>
-      <c r="B10" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="19"/>
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="70.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="28"/>
+      <c r="B10" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="20"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" s="1" customFormat="1" ht="76.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="21"/>
-      <c r="B11" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="20"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="17"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" s="1" customFormat="1" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="21"/>
-      <c r="B12" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="20"/>
+      <c r="A12" s="15"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="17"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A13" s="21"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="20"/>
+    <row r="13" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="15"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:10" ht="83.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="E14" s="20"/>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:10" ht="73.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="E15" s="20"/>
+      <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="E16" s="20"/>
+      <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="22"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A2:A13"/>
-    <mergeCell ref="C2:C13"/>
-    <mergeCell ref="D2:D13"/>
-    <mergeCell ref="E5:E16"/>
+    <mergeCell ref="A2:A10"/>
+    <mergeCell ref="E2:E10"/>
+    <mergeCell ref="C2:C10"/>
+    <mergeCell ref="D2:D10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/files/PingPongThread API Reference1.xlsx
+++ b/files/PingPongThread API Reference1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\source\pingpong\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892EB145-7FDC-4190-B7D5-16AF210A3985}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1152925-525F-4A5B-9A04-698C2F88C641}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PingPongThread" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,9 @@
     <sheet name="SingleStepsMotorOperation" sheetId="6" r:id="rId4"/>
     <sheet name="ScheduledStepsMotorOperation" sheetId="7" r:id="rId5"/>
     <sheet name="ScheduledPointsMotorOperation" sheetId="8" r:id="rId6"/>
+    <sheet name="ServoOperation" sheetId="10" r:id="rId7"/>
+    <sheet name="LEDMatrixOperation" sheetId="11" r:id="rId8"/>
+    <sheet name="CubeOperation" sheetId="12" r:id="rId9"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -127,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="141">
   <si>
     <t>Parameters</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -584,10 +587,6 @@
   </si>
   <si>
     <t>로봇 1개에 대한 스테퍼 모터를 작동시킨다. continue 모드, step 모드, schedule 모드를 담당한다. continue 모드는 스테퍼 모터가 계속 돌아가는 모드, step 모드는 특정한 스텝만큼만 모터가 돌아가는 모드, schedule 모드는 특정한 스케줄의 속도, 스텝을 가지고 스케줄 만큼 돌아가는 모드이다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테퍼 모터를 1개 이상으로 동시에 작동시킨다.  continue 모드, step 모드, schedule 모드를 담당한다. continue 모드는 스테퍼 모터가 계속 돌아가는 모드, step 모드는 특정한 스텝만큼만 모터가 돌아가는 모드, schedule 모드는 특정한 스케줄의 속도, 스텝을 가지고 스케줄 만큼 돌아가는 모드이다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1307,60 +1306,6 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>time_list=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: float or int or list or tuple or None
-time_option을 "step" 또는 "speed"로 잡았을 때, 스테퍼 모터를 돌릴 시간, 또는 시간의 스케줄. 단위는 초(sec)이다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>time_list=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: float or int or list or tuple or None
-time_option을 "step" 또는 "speed"로 잡았을 때, 스테퍼 모터를 돌릴 시간. 단위는 초(sec)이다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>sync=False</t>
     </r>
     <r>
@@ -1429,64 +1374,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>스테퍼 모터를 1개 이상으로 동시에 작동시킨다.  step 모드는 특정한 스텝만큼만 모터가 돌아가는 모드이다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>speed_list=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: float or int or list or tuple or None
-스테퍼 모터를 돌릴 속도의 스케줄. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. continue 모드에서 0이면 모터가 멈추고, step, schudule 모드에서 0이면 sleep 모드가 된다. 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 속도로 작동한다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>step_list=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: float or int or list or tuple or None
-스테퍼 모터를 돌릴 스텝의 스케줄. 단위가 바퀴(cycle)이면 범위는 0&lt;=step&lt;=32.7675이다. 단위가 스텝(STEP)이면 범위는 0&lt;=step&lt;=65535이다. sleep 모드이고 단위가 바퀴(CYCLE)이면 step 초(sec)만큼 쉬고, 범위는 0&lt;=step&lt;=65.535이다. sleep 모드이고 단위가 스텝(STEP)이면 step 밀리초(ms)만큼 쉬고, 범위는 0&lt;=step&lt;=65535이다. 디폴트(None)로 전달되면 단위가 바퀴(CYCLE)이면 1, 단위가 스텝(STEP)이면 2000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 스텝이 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 스텝으로 작동한다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>run_motor_schedule()</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1574,10 +1461,6 @@
   </si>
   <si>
     <t>로봇에 스테퍼 모터 스케줄을 설정한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>play_motor_schedule()</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1753,116 +1636,8 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">: float or int or list or tuple or None
-스테퍼 모터를 돌릴 속도, 또는 속도의 스케줄. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. continue 모드에서 0이면 모터가 멈추고, step, schudule 모드에서 0이면 sleep 모드가 된다. speed가 양수이면 시계방향, 음수이면 반시계방향으로 회전한다. 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 속도로 작동한다. </t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>step_list=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: float or int or list or tuple or None
-스테퍼 모터를 돌릴 스텝, 또는 스텝의 스케줄. 단위가 바퀴(cycle)이면 범위는 -32.7675&lt;=step&lt;=32.7675이다. 단위가 스텝(STEP)이면 범위는 -65535&lt;=step&lt;=65535이다. sleep 모드이고 단위가 바퀴(CYCLE)이면 step 초(sec)만큼 쉬고, 범위는 0&lt;=step&lt;=65.535이다. sleep 모드이고 단위가 스텝(STEP)이면 step 밀리초(ms)만큼 쉬고, 범위는 0&lt;=step&lt;=65535이다. 스텝이 음수이면 speed_list에서 정해진 방향에 반대로 회전한다. 디폴트(None)로 전달되면 단위가 바퀴(CYCLE)이면 1, 단위가 스텝(STEP)이면 2000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 스텝이 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 스텝으로 작동한다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>speed_list=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>: float or int or list or tuple or None
 스테퍼 모터를 돌릴 속도. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. speed가 양수이면 시계방향, 음수이면 반시계방향으로 회전한다 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 속도로 작동한다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>speed_list=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: float or int or list or tuple or None
-스테퍼 모터를 돌릴 속도. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. 0이면 sleep 모드가 된다. speed가 양수이면 시계방향, 음수이면 반시계방향으로 회전한다. 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 속도로 작동한다.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>step_list=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: float or int or list or tuple or None
-스테퍼 모터를 돌릴 스텝. 단위가 바퀴(cycle)이면 범위는 -32.7675&lt;=step&lt;=32.7675이다. 단위가 스텝(STEP)이면 범위는 -65535&lt;=step&lt;=65535이다. sleep 모드이고 단위가 바퀴(CYCLE)이면 step 초(sec)만큼 쉬고, 범위는 0&lt;=step&lt;=65.535이다. sleep 모드이고 단위가 스텝(STEP)이면 step 밀리초(ms)만큼 쉬고, 범위는 0&lt;=step&lt;=65535이다. 스텝이 음수이면 speed_list에서 정해진 방향에 반대로 회전한다. 디폴트(None)로 전달되면 단위가 바퀴(CYCLE)이면 1, 단위가 스텝(STEP)이면 2000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 스텝이 1개의 값만 전달되면, 모든 스테퍼 모터가 동일한 스텝으로 작동한다.</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1891,10 +1666,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>스테퍼 모터를 1개 이상으로 동시에 작동시킨다.  정한 schedule의 특정 부분을 재생시키는 스케줄을 짠다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -2007,24 +1778,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">run_motor()
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(expand에서 보수가 필요한가? 길이가 다른 경우.)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>stop_point_list=[[None]]</t>
     </r>
     <r>
@@ -2038,6 +1791,421 @@
       </rPr>
       <t>: list or tuple
 플레이 시킬 스케줄의 끝 인덱스의 리스트. 디폴트(None)이면 로봇에 지정된 스케줄의 끝의 인덱스로 설정된다. 인덱스를 "end"라고 하면 로봇에 지정한 스케줄의의 끝의 인덱스로 설정된다. 플레이는 이 끝의 인덱스를 포함하여 재생된다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>sync=False</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: bool</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>synchronize를 체크할 지 설정. True로 설정하면 각 큐브가 동일한 인덱스를 작동시키는지 체크한다. False로 설정하면 체크하지 않는다.
+(보수 필요?)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>discovery_group=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or None
+작동시킬 큐브의 소속 그룹 ID (1 to 8). None이면 그룹을 정하지 않는다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>run_motor()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테퍼 모터를 1개 이상으로 동시에 작동시킨다. continue 모드, step 모드, schedule 모드를 담당한다. continue 모드는 스테퍼 모터가 계속 돌아가는 모드, step 모드는 특정한 스텝만큼만 모터가 돌아가는 모드, schedule 모드는 특정한 스케줄의 속도, 스텝을 가지고 스케줄 만큼 돌아가는 모드이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>run_single_servo()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1개의 서보 모터를 작동시키는 함수.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>run_servo_schedule()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cube_ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: int or str
+작동시킬 서보 모터의 큐브 ID (1 to 8). "all"이면 모든 cube ID.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>angle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: int
+움직일 각도. 범위는  0 &lt;= angle &lt;= 180이고, 단위는 도(deg)이다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discovery_group=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or None
+작동시킬 큐브의 소속 그룹 ID (1 to 8). None이면 그룹을 정하지 않는다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>time_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+time_option을 "step" 또는 "speed"로 잡았을 때, 스테퍼 모터를 돌릴 시간, 또는 시간의 스케줄. 단위는 초(sec)이다. cube_ID_list에 큐브가 1개 이상인데 시간이 1개의 값(또는 1개의 스케줄)만 전달되면, 모든 스테퍼 모터가 동일한 시간(또는 동일한 스케줄)으로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>speed_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: float or int or list or tuple or None
+스테퍼 모터를 돌릴 속도, 또는 속도의 스케줄. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. continue 모드에서 0이면 모터가 멈추고, step, schudule 모드에서 0이면 sleep 모드가 된다. speed가 양수이면 시계방향, 음수이면 반시계방향으로 회전한다. 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값(또는 1개의 속도 스케줄)만 전달되면, 모든 스테퍼 모터가 동일한 속도(또는 동일한 속도 스케줄)로 작동한다. </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>step_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+스테퍼 모터를 돌릴 스텝, 또는 스텝의 스케줄. 단위가 바퀴(cycle)이면 범위는 -32.7675&lt;=step&lt;=32.7675이다. 단위가 스텝(STEP)이면 범위는 -65535&lt;=step&lt;=65535이다. sleep 모드이고 단위가 바퀴(CYCLE)이면 step 초(sec)만큼 쉬고, 범위는 0&lt;=step&lt;=65.535이다. sleep 모드이고 단위가 스텝(STEP)이면 step 밀리초(ms)만큼 쉬고, 범위는 0&lt;=step&lt;=65535이다. 스텝이 음수이면 speed_list에서 정해진 방향에 반대로 회전한다. 디폴트(None)로 전달되면 단위가 바퀴(CYCLE)이면 1, 단위가 스텝(STEP)이면 2000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 스텝이 1개의 값(또는 1개의 스텝 스케줄)만 전달되면, 모든 스테퍼 모터가 동일한 스텝(또는 동일한 스텝 스케줄)으로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>time_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+time_option을 "step" 또는 "speed"로 잡았을 때, 스테퍼 모터를 돌릴 시간, 또는 시간의 스케줄. 단위는 초(sec)이다. cube_ID_list에 큐브가 1개 이상인데 시간이 1개의 값(또는 1개의 시간 스케줄)만 전달되면, 모든 스테퍼 모터가 동일한 시간(또는 동일한 시간 스케줄)으로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>speed_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+스테퍼 모터를 돌릴 속도. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. 0이면 sleep 모드가 된다. speed가 양수이면 시계방향, 음수이면 반시계방향으로 회전한다. 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값(또는 1개의 속도 스케줄)만 전달되면, 모든 스테퍼 모터가 동일한 속도(또는 동일한 속도 스케줄)로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>step_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+스테퍼 모터를 돌릴 스텝. 단위가 바퀴(cycle)이면 범위는 -32.7675&lt;=step&lt;=32.7675이다. 단위가 스텝(STEP)이면 범위는 -65535&lt;=step&lt;=65535이다. sleep 모드이고 단위가 바퀴(CYCLE)이면 step 초(sec)만큼 쉬고, 범위는 0&lt;=step&lt;=65.535이다. sleep 모드이고 단위가 스텝(STEP)이면 step 밀리초(ms)만큼 쉬고, 범위는 0&lt;=step&lt;=65535이다. 스텝이 음수이면 speed_list에서 정해진 방향에 반대로 회전한다. 디폴트(None)로 전달되면 단위가 바퀴(CYCLE)이면 1, 단위가 스텝(STEP)이면 2000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 스텝이 1개의 값(또는 1개의 스텝 스케줄)만 전달되면, 모든 스테퍼 모터가 동일한 스텝(또는 동일한 스텝 스케줄)으로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>time_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+time_option을 "step" 또는 "speed"로 잡았을 때, 스테퍼 모터를 돌릴 시간. 단위는 초(sec)이다. cube_ID_list에 큐브가 1개 이상인데 시간이 1개의 값(또는 1개의 시간 스케줄)만 전달되면, 모든 스테퍼 모터가 동일한 시간(또는 동일한 시간 스케줄)으로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>speed_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+스테퍼 모터를 돌릴 속도의 스케줄. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. continue 모드에서 0이면 모터가 멈추고, step, schudule 모드에서 0이면 sleep 모드가 된다. 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 속도가 1개의 값(또는 1개의 속도 스케줄)만 전달되면, 모든 스테퍼 모터가 동일한 속도(또는 동일한 속도 스케줄)로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>step_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+스테퍼 모터를 돌릴 스텝의 스케줄. 단위가 바퀴(cycle)이면 범위는 0&lt;=step&lt;=32.7675이다. 단위가 스텝(STEP)이면 범위는 0&lt;=step&lt;=65535이다. sleep 모드이고 단위가 바퀴(CYCLE)이면 step 초(sec)만큼 쉬고, 범위는 0&lt;=step&lt;=65.535이다. sleep 모드이고 단위가 스텝(STEP)이면 step 밀리초(ms)만큼 쉬고, 범위는 0&lt;=step&lt;=65535이다. 디폴트(None)로 전달되면 단위가 바퀴(CYCLE)이면 1, 단위가 스텝(STEP)이면 2000으로 변환된다. cube_ID_list에 큐브가 1개 이상인데 스텝이 1개의 값(또는 1개의 스텝 스케줄)만 전달되면, 모든 스테퍼 모터가 동일한 스텝(또는 동일한 스텝 스케줄)으로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">play_motor_schedule()
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>repeat_list에 int 입력 가능하게 하면 좋을까?</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2047,9 +2215,9 @@
 repeat_list = [[1, 3], [2, 3, 3], [2]]
 start_point_list = [[0, 3], [2, 3, 4], [1]]
 stop_point_list = [[1, 6], [4, 5, 8], [1]]
-해석: 1번 큐브 스케줄 0번부터 1번까지 1번 반복, 3번부터 6번까지 3번 반복
-2번 큐브 스케줄 2번부터 4번까지 2번 반복, 3번부터 5번까지 3번 반복, 4번부터 8번까지 3번 반복
-3번 큐브 스케줄 1번만 2번 반복
+해석: (1번 큐브 스케줄 0번부터 1번까지 1번 반복, 3번부터 6번까지 3번 반복)
+(2번 큐브 스케줄 2번부터 4번까지 2번 반복, 3번부터 5번까지 3번 반복, 4번부터 8번까지 3번 반복)
+(3번 큐브 스케줄 1번만 2번 반복)
 Ex2)
 cube_ID_list = [1, 2, 4]
 repeat_list = [[1, 3], [2, 3, 3], [2]]
@@ -2059,27 +2227,307 @@
   </si>
   <si>
     <r>
-      <t>sync=False</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: bool</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>servo_angle_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or list or None
+서보 모터를 돌릴 각도, 또는 각도의 스케줄. 단위는 도(deg)이며, 범위는 0&lt;=angle&lt;=180이고, 정수 값만 가능하다. 디폴트(None)로 전달되면 에러가 발생된다. 스테퍼 값(또는 스케줄)이 입력되면 스테퍼의 각각의 움직임이 시작할 때 서보도 같이 움직이며, 따라서 servo_angle_list는 스테퍼 스케줄의 길이와 동일해야 한다. cube_ID_list에 큐브가 1개 이상인데 각도가 1개의 값(또는 1개의 각도 스케줄)만 전달되면, 모든 서보 모터가 동일한 각도(또는 동일한 각도 스케줄)로 작동한다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>speed_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+스테퍼 모터를 돌릴 속도, 또는 속도의 스케줄. 단위가 RPM이면, 범위는 -30&lt;=speed&lt;=-3, speed=0, 3&lt;=speed&lt;=30이다. 단위가 SPS이면 범위는 -1000&lt;=speed&lt;=-100, speed=0, 100&lt;=speed&lt;=1000이다. speed가 0이면 sleep 모드가 된다. 디폴트(None)로 전달되면 단위가 RPM이면 30, 단위가 SPS면 1000으로 변환된다. speed_list가 입력되면 스케줄 길이는 servo_angle_list의 스케줄 길이와 동일해야 한다. cube_ID_list에 큐브가 1개 초과인데 속도가 1개의 값(또는 1개의 속도 스케줄)만 전달되면, 모든 스테퍼 모터가 동일한 속도(또는 동일한 속도 스케줄)로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>step_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+스테퍼 모터를 돌릴 스텝의 스케줄. 단위가 바퀴(cycle)이면 범위는 0&lt;=step&lt;=32.7675이다. 단위가 스텝(STEP)이면 범위는 0&lt;=step&lt;=65535이다. sleep 모드이고 단위가 바퀴(CYCLE)이면 step 초(sec)만큼 쉬고, 범위는 0&lt;=step&lt;=65.535이다. sleep 모드이고 단위가 스텝(STEP)이면 step 밀리초(ms)만큼 쉬고, 범위는 0&lt;=step&lt;=65535이다. 디폴트(None)로 전달되면 단위가 바퀴(CYCLE)이면 1, 단위가 스텝(STEP)이면 2000으로 변환된다. step_list가 입력되면 스케줄 길이는 servo_angle_list의 스케줄 길이와 동일해야 한다. cube_ID_list에 큐브가 1개 이상인데 스텝이 1개의 값(또는 1개의 스텝 스케줄)만 전달되면, 모든 스테퍼 모터가 동일한 스텝(또는 동일한 스텝 스케줄)으로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>servo_duration=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or list or None
+서보 모터를 돌릴 동안 기다릴 시간, 또는 기다릴 시간의 스케줄. 단위는 초이며, 범위는 0&lt;=duration&lt;=65.535이다. 디폴트(None)로 전달되면 모든 각도(또는 각도 스케줄)를 1초 동안 기다린다. servo_duration에 값이 입력되면(디폴트가 아니면) speed_list, step_list, time_list는 무시된다. cube_ID_list에 큐브가 1개 이상인데 시간이 1개의 값(또는 1개의 시간 스케줄)만 전달되면, 모든 서보 모터가 동일한 시간(또는 동일한 각도 스케줄)동안 기다린다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>time_list=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int or list or tuple or None
+time_option을 "step" 또는 "speed"로 잡았을 때, 스테퍼 모터를 돌릴 시간, 또는 시간의 스케줄. 단위는 초(sec)이다.  time_list가 입력되면 스케줄 길이는 servo_angle_list의 스케줄 길이와 동일해야 한다. cube_ID_list에 큐브가 1개 이상인데 시간이 1개의 값(또는 1개의 스케줄)만 전달되면, 모든 스테퍼 모터가 동일한 시간(또는 동일한 스케줄)으로 작동한다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테퍼 모터를 1개 이상으로 동시에 작동시킨다. step 모드는 특정한 스텝만큼만 모터가 돌아가는 모드이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테퍼 모터를 1개 이상으로 동시에 작동시킨다. schedule 모드는 특정한 스케줄의 속도, 스텝을 가지고 스케줄 만큼 돌아가는 모드이다.</t>
+  </si>
+  <si>
+    <t>서보 모터를 1개 이상으로 동시에 작동시킨다. 스테퍼 모터와 동시에 작동시킬 수도 있다. servo_duration으로 서보 모터가 움직이는 동안 기다리는 시간을 설정할 수 있고, servo_duration를 입력시키면 스테퍼 모터는 작동시킬 수 없다. servo_duration을 입력시키지 않고 스테퍼 모터의 스케줄을 입력시키면, 스테퍼 모터의 각각의 움직임이 시작될 때 서보 모터도 같이 작동되며, 따라서 스테퍼 모터의 스케줄의 길이와 서보 모터의 스케줄의 길이는 동일해야 한다.</t>
+  </si>
+  <si>
+    <t>Ex1)
+cube_ID_list = [1, 3, 4]
+servo_angle_list = [[0, 90, 180]]
+servo_duration = [[1, 1, 2], [2, 1, 2], [1, 1, 1]]
+Ex2)
+cube_ID_list = [1, 3, 4]
+servo_angle_list = [[0, 90, 180], [90, 0, 180], [180, 90, 180]]
+speed_list = [[15, 30, -15], [30, -30, 0], [-15, 15, -15]]
+step_list = [[1, 2, 3], [2, 1, 3], [-1, -1, -1]]
+Ex3)
+cube_ID_list = [1, 3, 4]
+servo_angle_list = [[0, 90, 180], [90, 0, 180], [180, 90, 180]]
+speed_list = [[15, 30, -15], [30, -30, 0], [-15, 15, -15]]
+time_list = [[1, 1, 1]]
+time_option = "speed"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>set_servo_schedule()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>return</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; None</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">cube_ID_list="all", servo_angle_list=None, servo_duration=None, pause_list=True, speed_list=None, step_list=None, time_list=None, discovery_group=None, speed_option="RPM", step_option="CYCLE", sync=False, time_option=None, wait=0
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>run_servo_schedule() 함수와 완전히 동일하며, pause_list의 디폴트 값만 True이다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇에 서보 모터 스케줄을 설정한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">play_servo_schedule()
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>repeat_list에 int 입력 가능하게 하면 좋을까?</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇에 입력된 서보, 스테퍼 스케줄을 이용하여 로봇을 1개 이상으로 동시에 작동시킨다. 입력된 서보, 스테퍼 스케줄의 특정 부분을 재생시키는 스케줄을 짜서 작동시키는 방식이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇에 입력된 스테퍼 스케줄을 이용하여 로봇을 1개 이상으로 동시에 작동시킨다. 입력된 스테퍼 스케줄의 특정 부분을 재생시키는 스케줄을 짜서 작동시키는 방식이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LED_matrix_write_pixel()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cube_ID_list</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or str
+작동시킬 모터의 큐브 ID (1 to 8). "all"이면 모든 cube ID.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LED_matrix_write_string()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LED matrix의 한 개의 불빛을 조작한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LED matrix에 글자를 표시한다. 글자는 scroll_time 시간동안 오른쪽에서 왼쪽으로 지나간다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cube_ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or str</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -2094,13 +2542,91 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>synchronize를 체크할 지 설정. True로 설정하면 각 큐브가 동일한 인덱스를 작동시키는지 체크한다. False로 설정하면 체크하지 않는다.
-(보수 필요?)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
+      <t>작동시킬 LED matrix의 큐브 ID (1 to 8). "all"이면 모든 cube ID.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+x_coordinate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: int
+LED matrix의 불빛을 조작할 LED의 x좌표. 범위는 0~7이며, 정수값이다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>y_coordinate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: int
+LED matrix의 불빛을 조작할 LED의 y좌표. 범위는 0~7이며, 정수값이다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>onoff=True</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: bool
+LED matrix의 불빛을 조작할 LED의 on/off 여부. True이면 불을 켜고, False이면 불을 끈다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>discovery_group=None</t>
     </r>
     <r>
@@ -2108,13 +2634,683 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: int or None
-작동시킬 큐브의 소속 그룹 ID (1 to 8). None이면 그룹을 정하지 않는다.</t>
-    </r>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or str
+LED matrix를 조작할 로봇이 소속된 그룹 ID (1 to 8). None이면 그룹을 정하지 않는다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cube_ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: int or str
+작동시킬 LED matrix의 큐브 ID (1 to 8). "all"이면 모든 cube ID.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: str
+LED matrix에 쓸 문자. 문자의 길이는 1~20이며, ASCII 문자만 표시시킬 수 있다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>scroll_time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: int or float
+LED matrix에 쓸 문자가 지나가는 시간. 단위는 초(sec)이다. (scroll_time / string_length * 8)의 최대는 200, 최소는 1을 넘지 못한다. 저 값이 최대를 넘으면 200, 최소를 넘으면 0으로 설정된다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discovery_group=None:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> int or str</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LED matrix</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>조작할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>로봇이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>소속된</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>그룹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ID (1 to 8). None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>그룹을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>정하지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LED_matrix_clear()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LED_matrix_write_picture()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>cube_ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or str
+LED matrix의 큐브 ID (1 to 8). "all"이면 모든 cube ID.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+discovery_group=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or str
+LED matrix를 조작할 로봇이 소속된 그룹 ID (1 to 8). None이면 그룹을 정하지 않는다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LED matrix에 그림을 그린다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LED matrix의 불빛을 모두 끈다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>picture = [
+[0, 0, 0, 0, 0, 0, 0, 0],
+[0, 0, 0, 0, 0, 0, 1, 0],
+[1, 1, 1, 1, 1, 0, 1, 0],
+[0, 0, 0, 1, 0, 0, 1, 0],
+[0, 0, 1, 1, 0, 0, 1, 1],
+[0, 1, 1, 0, 0, 0, 1, 0],
+[1, 1, 0, 0, 0, 0, 1, 0],
+[0, 0, 0, 0, 0, 0, 1, 0]]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cube_ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: int or str
+작동시킬 LED matrix의 큐브 ID (1 to 8). "all"이면 모든 cube ID.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>picture</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: list
+LED matrix에 그릴 그림. 8 by 8의 행렬(list of list)이다. 원소는 0, 또는 1이며, 0이면 불이 꺼지고 1이면 불이 켜진다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discovery_group=Non</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>e: int or str
+LED matrix를 조작할 로봇이 소속된 그룹 ID (1 to 8). None이면 그룹을 정하지 않는다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>receive_sensor_data()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stop_sensor_data()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cube_ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or str
+센서 값을 받을 로봇의 큐브 ID (1 to 8). "all"이면 모든 cube ID.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+discovery_group=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or str
+센서 값을 받을 로봇이 소속된 그룹 ID (1 to 8). None이면 그룹을 정하지 않는다.</t>
+    </r>
+  </si>
+  <si>
+    <t>주기적으로 받는 센서 값을 더 이상 받지 않는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cube_ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or str</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>센서 값을 받을 로봇의 큐브 ID (1 to 8). "all"이면 모든 cube ID.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+method</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: str</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>센서 값을 받는 방법. "oneshot", "periodic", "stop"이 있다. "oneshot"은 센서 값을 한 번만 받는 것, "periodic"은 센서 값을 주기적으로 계속 받는 것, "stop"은 periodic을 그만 받는 것이다. "oneshot"은 periodic 모드일 때 보내면 에러가 발생하고, "stop"은 periodic 모드가 아닐 때 에러가 발생한다.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+period=1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or float
+periodic 모드에서 센서 값을 받을 주기. 단위는 초이며, 범위는 0.01~1이다.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+discovery_group=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or str
+센서 값을 받을 로봇이 소속된 그룹 ID (1 to 8). None이면 그룹을 정하지 않는다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>센서 값을 받는다. 한 번 받을 수도 있고, 주기적으로 계속 받을 수도 있다.
+받는 값은 총 9개로, 버튼(button), 자이로 센서 xyz(sensor_gyro_xyz), 가속도 센서 xyz(sensor_acc_xyz), 근접 센서(sensor_prox), 외부 센서(AIN)이다. 외부 센서에는 소리 센서, 조도 센서 등이 있다. 로봇에 외부 센서를 꽂지 않았으면 무시하면 된다.
+받은 값은 robotstatus에 저장되며, 누적되지는 않는다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2122,7 +3318,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2227,6 +3423,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2278,7 +3482,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2340,6 +3544,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2358,11 +3577,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2379,6 +3598,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1884218</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>387927</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3288584</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1814944</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A944FD3-04D7-40A8-87DA-92F68D7FB225}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19160836" y="6165272"/>
+          <a:ext cx="1404366" cy="1427017"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2670,7 +3938,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -2704,7 +3972,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>16</v>
@@ -2740,7 +4008,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>17</v>
@@ -2754,7 +4022,7 @@
         <v>19</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>16</v>
@@ -2771,7 +4039,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>22</v>
@@ -2788,7 +4056,7 @@
         <v>24</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>32</v>
@@ -2805,7 +4073,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>33</v>
@@ -2869,7 +4137,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -2881,7 +4149,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>13</v>
@@ -2895,7 +4163,7 @@
         <v>36</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>34</v>
@@ -2909,7 +4177,7 @@
         <v>37</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>34</v>
@@ -2919,146 +4187,146 @@
       </c>
     </row>
     <row r="5" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="21" t="s">
-        <v>97</v>
+      <c r="A5" s="26" t="s">
+        <v>88</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="25"/>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="102.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="26"/>
+      <c r="B6" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="25"/>
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="115.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="26"/>
+      <c r="B7" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="27"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="25"/>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="26"/>
+      <c r="B8" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="20"/>
-    </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" ht="102.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="21"/>
-      <c r="B6" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="20"/>
-    </row>
-    <row r="7" spans="1:10" s="1" customFormat="1" ht="115.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="21"/>
-      <c r="B7" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="20"/>
-    </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="21"/>
-      <c r="B8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="20"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="25"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" s="1" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="21"/>
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="67.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="26"/>
       <c r="B9" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="20"/>
+        <v>97</v>
+      </c>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="25"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="21"/>
+      <c r="A10" s="26"/>
       <c r="B10" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="20"/>
+        <v>47</v>
+      </c>
+      <c r="C10" s="27"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="25"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" s="1" customFormat="1" ht="67.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="21"/>
+      <c r="A11" s="26"/>
       <c r="B11" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="20"/>
+        <v>52</v>
+      </c>
+      <c r="C11" s="27"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="25"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" s="1" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="21"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="20"/>
+        <v>53</v>
+      </c>
+      <c r="C12" s="27"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="25"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A13" s="21"/>
+      <c r="A13" s="26"/>
       <c r="B13" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="20"/>
+        <v>54</v>
+      </c>
+      <c r="C13" s="27"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="25"/>
     </row>
     <row r="14" spans="1:10" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="21"/>
+      <c r="A14" s="26"/>
       <c r="B14" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="27"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="25"/>
+    </row>
+    <row r="15" spans="1:10" ht="49.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="26"/>
+      <c r="B15" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="20"/>
-    </row>
-    <row r="15" spans="1:10" ht="49.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="21"/>
-      <c r="B15" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="20"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="25"/>
     </row>
     <row r="16" spans="1:10" ht="56.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="21"/>
+      <c r="A16" s="26"/>
       <c r="B16" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="20"/>
+        <v>67</v>
+      </c>
+      <c r="C16" s="27"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="25"/>
     </row>
     <row r="17" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C17" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -3102,7 +4370,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -3110,66 +4378,66 @@
       <c r="J1" s="8"/>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="26"/>
+      <c r="B3" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="27"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="25"/>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="26"/>
+      <c r="B4" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="25"/>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="26"/>
+      <c r="B5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="25"/>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="26"/>
+      <c r="B6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="25"/>
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="26"/>
+      <c r="B7" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="21"/>
-      <c r="B3" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="20"/>
-    </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="21"/>
-      <c r="B4" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="20"/>
-    </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="21"/>
-      <c r="B5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="20"/>
-    </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="21"/>
-      <c r="B6" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="20"/>
-    </row>
-    <row r="7" spans="1:10" s="1" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="21"/>
-      <c r="B7" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="20"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="25"/>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="136.19999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="15"/>
@@ -3250,7 +4518,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{456CB50E-7EFD-4EF4-8117-80D93E52D2D4}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.59765625" style="4" customWidth="1"/>
@@ -3276,7 +4544,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -3284,155 +4552,149 @@
       <c r="J1" s="8"/>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="21" t="s">
-        <v>65</v>
+      <c r="A2" s="26" t="s">
+        <v>64</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="88.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="26"/>
+      <c r="B3" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="27"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="25"/>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="114.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="26"/>
+      <c r="B4" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="25"/>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="26"/>
+      <c r="B5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" ht="88.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="21"/>
-      <c r="B3" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="20"/>
-    </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="108.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="21"/>
-      <c r="B4" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="20"/>
-    </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="21"/>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="27"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="25"/>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="50.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="26"/>
+      <c r="B6" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="25"/>
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="26"/>
+      <c r="B7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="20"/>
-    </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="21"/>
-      <c r="B6" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="20"/>
-    </row>
-    <row r="7" spans="1:10" s="1" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="21"/>
-      <c r="B7" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="20"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="25"/>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="21"/>
+      <c r="A8" s="26"/>
       <c r="B8" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="20"/>
+        <v>53</v>
+      </c>
+      <c r="C8" s="27"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="25"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="21"/>
+      <c r="A9" s="26"/>
       <c r="B9" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="20"/>
+        <v>54</v>
+      </c>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="25"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" s="1" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="21"/>
+      <c r="A10" s="26"/>
       <c r="B10" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="20"/>
+        <v>65</v>
+      </c>
+      <c r="C10" s="27"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="25"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" s="1" customFormat="1" ht="57.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="21"/>
+      <c r="A11" s="26"/>
       <c r="B11" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="20"/>
+        <v>57</v>
+      </c>
+      <c r="C11" s="27"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="25"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" s="1" customFormat="1" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="21"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="20"/>
+        <v>66</v>
+      </c>
+      <c r="C12" s="27"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="25"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A13" s="21"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="20"/>
-    </row>
-    <row r="14" spans="1:10" ht="83.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" ht="73.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:10" ht="73.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="3"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="18"/>
-    </row>
-    <row r="18" spans="1:4" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:10" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="3"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="18"/>
+    </row>
+    <row r="17" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A2:A13"/>
-    <mergeCell ref="C2:C13"/>
-    <mergeCell ref="D2:D13"/>
-    <mergeCell ref="E2:E13"/>
+    <mergeCell ref="A2:A12"/>
+    <mergeCell ref="C2:C12"/>
+    <mergeCell ref="D2:D12"/>
+    <mergeCell ref="E2:E12"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3445,7 +4707,7 @@
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.59765625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="69.8984375" customWidth="1"/>
+    <col min="2" max="2" width="115.5" customWidth="1"/>
     <col min="3" max="3" width="48.59765625" customWidth="1"/>
     <col min="4" max="4" width="46.3984375" customWidth="1"/>
     <col min="5" max="5" width="58" customWidth="1"/>
@@ -3467,7 +4729,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -3475,145 +4737,145 @@
       <c r="J1" s="8"/>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="21" t="s">
-        <v>74</v>
+      <c r="A2" s="26" t="s">
+        <v>68</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="87.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="26"/>
+      <c r="B3" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="27"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="25"/>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="107.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="26"/>
+      <c r="B4" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="25"/>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="26"/>
+      <c r="B5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" ht="124.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="21"/>
-      <c r="B3" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="20"/>
-    </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="159.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="21"/>
-      <c r="B4" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="20"/>
-    </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="21"/>
-      <c r="B5" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="20"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="25"/>
     </row>
     <row r="6" spans="1:10" s="1" customFormat="1" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="21"/>
+      <c r="A6" s="26"/>
       <c r="B6" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="20"/>
+        <v>94</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="25"/>
     </row>
     <row r="7" spans="1:10" s="1" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="21"/>
+      <c r="A7" s="26"/>
       <c r="B7" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="20"/>
+        <v>83</v>
+      </c>
+      <c r="C7" s="27"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="25"/>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="21"/>
+      <c r="A8" s="26"/>
       <c r="B8" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="20"/>
+        <v>53</v>
+      </c>
+      <c r="C8" s="27"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="25"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="21"/>
+      <c r="A9" s="26"/>
       <c r="B9" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="20"/>
+        <v>54</v>
+      </c>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="25"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" s="1" customFormat="1" ht="70.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="21"/>
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="58.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="26"/>
       <c r="B10" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="20"/>
+        <v>69</v>
+      </c>
+      <c r="C10" s="27"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="25"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" s="1" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="21"/>
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26"/>
       <c r="B11" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="20"/>
+        <v>57</v>
+      </c>
+      <c r="C11" s="27"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="25"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" s="1" customFormat="1" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="21"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="20"/>
+        <v>70</v>
+      </c>
+      <c r="C12" s="27"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="25"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A13" s="21"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="20"/>
-    </row>
-    <row r="14" spans="1:10" ht="87.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="26"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="25"/>
+    </row>
+    <row r="14" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E14" s="1"/>
     </row>
@@ -3671,7 +4933,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -3679,99 +4941,99 @@
       <c r="J1" s="8"/>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="32"/>
+      <c r="B3" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="27"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="25"/>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="50.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="32"/>
+      <c r="B4" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="28"/>
-      <c r="B3" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="20"/>
-    </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="50.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="28"/>
-      <c r="B4" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="20"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="25"/>
     </row>
     <row r="5" spans="1:10" s="1" customFormat="1" ht="70.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="28"/>
-      <c r="B5" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="20"/>
+      <c r="A5" s="32"/>
+      <c r="B5" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="25"/>
     </row>
     <row r="6" spans="1:10" s="1" customFormat="1" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="28"/>
-      <c r="B6" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="20"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="25"/>
     </row>
     <row r="7" spans="1:10" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="28"/>
-      <c r="B7" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="20"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="27"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="25"/>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="28"/>
-      <c r="B8" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="20"/>
+      <c r="A8" s="32"/>
+      <c r="B8" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="27"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="25"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" s="1" customFormat="1" ht="73.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="28"/>
-      <c r="B9" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="20"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="25"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" s="1" customFormat="1" ht="70.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="28"/>
+      <c r="A10" s="32"/>
       <c r="B10" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="20"/>
+        <v>67</v>
+      </c>
+      <c r="C10" s="27"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="25"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -3825,4 +5087,600 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08E485FD-6601-4AAC-B2BD-04F4962E9976}">
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="44.59765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="112.796875" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="4" max="4" width="46.3984375" customWidth="1"/>
+    <col min="5" max="5" width="52.796875" customWidth="1"/>
+    <col min="6" max="7" width="12.69921875" customWidth="1"/>
+    <col min="8" max="10" width="15.19921875" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.65">
+      <c r="A1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="110.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="91.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="26"/>
+      <c r="B4" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="25"/>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="89.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="26"/>
+      <c r="B5" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="25"/>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="26"/>
+      <c r="B6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="25"/>
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="105.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="26"/>
+      <c r="B7" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="27"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="25"/>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="124.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="26"/>
+      <c r="B8" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="27"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="25"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="26"/>
+      <c r="B9" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="25"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="26"/>
+      <c r="B10" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="27"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="25"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26"/>
+      <c r="B11" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="27"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="25"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="27"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="25"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="26"/>
+      <c r="B13" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="27"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="25"/>
+    </row>
+    <row r="14" spans="1:10" ht="60.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="26"/>
+      <c r="B14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="27"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="25"/>
+    </row>
+    <row r="15" spans="1:10" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A15" s="26"/>
+      <c r="B15" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="17" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A18" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" s="31" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A19" s="32"/>
+      <c r="B19" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="27"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="25"/>
+    </row>
+    <row r="20" spans="1:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A20" s="32"/>
+      <c r="B20" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="27"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="25"/>
+    </row>
+    <row r="21" spans="1:5" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A21" s="32"/>
+      <c r="B21" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="27"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="25"/>
+    </row>
+    <row r="22" spans="1:5" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="32"/>
+      <c r="B22" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="27"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="25"/>
+    </row>
+    <row r="23" spans="1:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A23" s="32"/>
+      <c r="B23" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="27"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="25"/>
+    </row>
+    <row r="24" spans="1:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A24" s="32"/>
+      <c r="B24" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" s="27"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="25"/>
+    </row>
+    <row r="25" spans="1:5" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="32"/>
+      <c r="B25" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="27"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="25"/>
+    </row>
+    <row r="26" spans="1:5" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A26" s="32"/>
+      <c r="B26" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="27"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A18:A26"/>
+    <mergeCell ref="C18:C26"/>
+    <mergeCell ref="D18:D26"/>
+    <mergeCell ref="E18:E26"/>
+    <mergeCell ref="C3:C14"/>
+    <mergeCell ref="D3:D14"/>
+    <mergeCell ref="E3:E14"/>
+    <mergeCell ref="A3:A15"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6985C73-1DB2-44E6-B6F5-97BBE8D4446C}">
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="44.59765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="87.296875" customWidth="1"/>
+    <col min="3" max="3" width="48.59765625" customWidth="1"/>
+    <col min="4" max="4" width="46.3984375" customWidth="1"/>
+    <col min="5" max="5" width="48.69921875" customWidth="1"/>
+    <col min="6" max="7" width="12.69921875" customWidth="1"/>
+    <col min="8" max="10" width="15.19921875" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.65">
+      <c r="A1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="187.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="159" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="172.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="11"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="22"/>
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="11"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="22"/>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="11"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="6"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+    </row>
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="11"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+    </row>
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="11"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+    </row>
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="11"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+    </row>
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="11"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="6"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2080388C-13B8-4E16-880C-F0B494742D61}">
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="44.59765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="87.296875" customWidth="1"/>
+    <col min="3" max="3" width="48.59765625" customWidth="1"/>
+    <col min="4" max="4" width="48.3984375" customWidth="1"/>
+    <col min="5" max="5" width="48.69921875" customWidth="1"/>
+    <col min="6" max="7" width="12.69921875" customWidth="1"/>
+    <col min="8" max="10" width="15.19921875" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.65">
+      <c r="A1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="193.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="11"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="24"/>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="172.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="23"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="11"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="22"/>
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="11"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="22"/>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="11"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="6"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+    </row>
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="11"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+    </row>
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="11"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+    </row>
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="11"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+    </row>
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="11"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="6"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/files/PingPongThread API Reference1.xlsx
+++ b/files/PingPongThread API Reference1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\source\pingpong\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1152925-525F-4A5B-9A04-698C2F88C641}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D5A396-D11B-4557-AA9B-9F084C948DEE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -130,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="146">
   <si>
     <t>Parameters</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -374,32 +374,6 @@
   </si>
   <si>
     <t>wait()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>time_seconds</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: float or int
-기다릴 시간. 단위는 초(sec).</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -744,58 +718,6 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>RPM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: float or int
-RPM 단위의 스테퍼 모터 속도. 범위는 -30&lt;=RPM&lt;=-3, RPM=0, 3&lt;=RPM&lt;=30.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SPS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: int
-SPS 단위의 스테퍼 모터 속도. 범위는 -1000&lt;=SPS&lt;=-100, SPS=0, 100&lt;=SPS&lt;=1000.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>cube_ID_list</t>
     </r>
     <r>
@@ -875,95 +797,6 @@
       </rPr>
       <t>:
 작동시킬 큐브의 소속 그룹 ID (1 to 8). None이면 그룹을 정하지 않음.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>discovery_group=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: int or None
-스테이터스를 얻을 그룹 ID (1 to 8). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>None이면 그룹을 정하지 않음.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>discovery_group=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: int or None
-연결을 기다릴 그룹 ID (1 to 8). None이면 그룹을 정하지 않음.</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>discovery_group=None</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: int or None
-연결과 관련된 그룹 ID (1 to 8). None이면 그룹을 정하지 않음.</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3308,8 +3141,243 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>__getitem__()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>status 값을 얻는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>time_seconds</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int
+기다릴 시간. 단위는 초(sec)이다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RPM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: float or int
+RPM 단위의 스테퍼 모터 속도. 범위는 -30&lt;=RPM&lt;=-3, RPM=0, 3&lt;=RPM&lt;=30 이다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int
+SPS 단위의 스테퍼 모터 속도. 범위는 -1000&lt;=SPS&lt;=-100, SPS=0, 100&lt;=SPS&lt;=1000 이다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discovery_group=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or None
+연결과 관련된 그룹 ID (1 to 8). None이면 그룹을 정하지 않는다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discovery_group=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: int or None
+연결을 기다릴 그룹 ID (1 to 8). None이면 그룹을 정하지 않는다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discovery_group=None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: int or None
+스테이터스를 얻을 그룹 ID (1 to 8). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>None이면 그룹을 정하지 않는다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>return</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; list</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연결할 숫자:
+PingPongThreadInstance["connection_number"]
+스테퍼 모터 속도:
+PingPongThreadInstance["stepper_speed"]
+등등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: str
+status에서 얻을 값. 큐브 ID의 순서대로 리스트로 나타난다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>센서 값을 받는다. 한 번 받을 수도 있고, 주기적으로 계속 받을 수도 있다.
-받는 값은 총 9개로, 버튼(button), 자이로 센서 xyz(sensor_gyro_xyz), 가속도 센서 xyz(sensor_acc_xyz), 근접 센서(sensor_prox), 외부 센서(AIN)이다. 외부 센서에는 소리 센서, 조도 센서 등이 있다. 로봇에 외부 센서를 꽂지 않았으면 무시하면 된다.
+받는 값은 총 9개로, 버튼(button), 자이로 센서 xyz(sensor_gyro_xyz), 가속도 센서 xyz(sensor_acc_xyz), 근접 센서(sensor_prox), 외부 센서(AIN)이다. 외부 센서에는 소리 센서, 조도 센서 등이 있다. 로봇에 외부 센서를 꽂지 않았으면, AIN은 무시하면 된다.
 받은 값은 robotstatus에 저장되며, 누적되지는 않는다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3556,6 +3624,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3579,9 +3650,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3912,7 +3980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="44.59765625" style="4" customWidth="1"/>
@@ -3938,7 +4006,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -3972,7 +4040,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>16</v>
@@ -3983,7 +4051,7 @@
     </row>
     <row r="5" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>13</v>
@@ -4008,7 +4076,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>17</v>
@@ -4022,7 +4090,7 @@
         <v>19</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>16</v>
@@ -4039,7 +4107,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>22</v>
@@ -4051,15 +4119,15 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="11" t="s">
         <v>24</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>43</v>
+        <v>137</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>25</v>
@@ -4068,15 +4136,15 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>27</v>
@@ -4090,17 +4158,34 @@
         <v>28</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>29</v>
+        <v>136</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" ht="85.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>143</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4137,7 +4222,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -4146,187 +4231,187 @@
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="280.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" ht="109.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="107.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="26" t="s">
-        <v>88</v>
+      <c r="A5" s="27" t="s">
+        <v>82</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="26"/>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="102.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="27"/>
+      <c r="B6" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E5" s="25"/>
-    </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" ht="102.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="26"/>
-      <c r="B6" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="25"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="26"/>
     </row>
     <row r="7" spans="1:10" s="1" customFormat="1" ht="115.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="26"/>
+      <c r="A7" s="27"/>
       <c r="B7" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C7" s="27"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="25"/>
+        <v>90</v>
+      </c>
+      <c r="C7" s="28"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="26"/>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="26"/>
+      <c r="A8" s="27"/>
       <c r="B8" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="25"/>
+        <v>43</v>
+      </c>
+      <c r="C8" s="28"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="26"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" s="1" customFormat="1" ht="67.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="26"/>
+      <c r="A9" s="27"/>
       <c r="B9" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="25"/>
+        <v>91</v>
+      </c>
+      <c r="C9" s="28"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="26"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="26"/>
+      <c r="A10" s="27"/>
       <c r="B10" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="25"/>
+        <v>44</v>
+      </c>
+      <c r="C10" s="28"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="26"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" s="1" customFormat="1" ht="67.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="26"/>
+      <c r="A11" s="27"/>
       <c r="B11" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="25"/>
+        <v>46</v>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="26"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" s="1" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="26"/>
+      <c r="A12" s="27"/>
       <c r="B12" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="25"/>
+        <v>47</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="26"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A13" s="26"/>
+      <c r="A13" s="27"/>
       <c r="B13" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="25"/>
+        <v>48</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:10" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="26"/>
+      <c r="A14" s="27"/>
       <c r="B14" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="25"/>
+        <v>50</v>
+      </c>
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="26"/>
     </row>
     <row r="15" spans="1:10" ht="49.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="26"/>
+      <c r="A15" s="27"/>
       <c r="B15" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="25"/>
+        <v>51</v>
+      </c>
+      <c r="C15" s="28"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="26"/>
     </row>
     <row r="16" spans="1:10" ht="56.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="26"/>
+      <c r="A16" s="27"/>
       <c r="B16" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="25"/>
+        <v>61</v>
+      </c>
+      <c r="C16" s="28"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="26"/>
     </row>
     <row r="17" spans="1:4" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -4370,7 +4455,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -4378,66 +4463,66 @@
       <c r="J1" s="8"/>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="29" t="s">
-        <v>61</v>
+      <c r="A2" s="30" t="s">
+        <v>55</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>74</v>
+      <c r="D2" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="26"/>
+      <c r="A3" s="27"/>
       <c r="B3" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="25"/>
+        <v>70</v>
+      </c>
+      <c r="C3" s="28"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="26"/>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="26"/>
+      <c r="A4" s="27"/>
       <c r="B4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="25"/>
+        <v>43</v>
+      </c>
+      <c r="C4" s="28"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="26"/>
     </row>
     <row r="5" spans="1:10" s="1" customFormat="1" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="26"/>
+      <c r="A5" s="27"/>
       <c r="B5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="26"/>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="27"/>
+      <c r="B6" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="25"/>
-    </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="26"/>
-      <c r="B6" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="25"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="26"/>
     </row>
     <row r="7" spans="1:10" s="1" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="26"/>
+      <c r="A7" s="27"/>
       <c r="B7" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="27"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="25"/>
+        <v>56</v>
+      </c>
+      <c r="C7" s="28"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="26"/>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="136.19999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="15"/>
@@ -4544,7 +4629,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -4552,123 +4637,123 @@
       <c r="J1" s="8"/>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="26" t="s">
-        <v>64</v>
+      <c r="A2" s="27" t="s">
+        <v>58</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>77</v>
+      <c r="D2" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" ht="88.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="26"/>
+      <c r="A3" s="27"/>
       <c r="B3" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="25"/>
+        <v>92</v>
+      </c>
+      <c r="C3" s="28"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="26"/>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="114.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="26"/>
+      <c r="A4" s="27"/>
       <c r="B4" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="25"/>
+        <v>93</v>
+      </c>
+      <c r="C4" s="28"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="26"/>
     </row>
     <row r="5" spans="1:10" s="1" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="26"/>
+      <c r="A5" s="27"/>
       <c r="B5" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="25"/>
+        <v>43</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="26"/>
     </row>
     <row r="6" spans="1:10" s="1" customFormat="1" ht="50.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="26"/>
+      <c r="A6" s="27"/>
       <c r="B6" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="25"/>
+        <v>94</v>
+      </c>
+      <c r="C6" s="28"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="26"/>
     </row>
     <row r="7" spans="1:10" s="1" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="26"/>
+      <c r="A7" s="27"/>
       <c r="B7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="28"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="26"/>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="27"/>
+      <c r="B8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="27"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="25"/>
-    </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="26"/>
-      <c r="B8" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="25"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="26"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="26"/>
+      <c r="A9" s="27"/>
       <c r="B9" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="25"/>
+        <v>48</v>
+      </c>
+      <c r="C9" s="28"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="26"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" s="1" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="26"/>
+      <c r="A10" s="27"/>
       <c r="B10" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="25"/>
+        <v>59</v>
+      </c>
+      <c r="C10" s="28"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="26"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" s="1" customFormat="1" ht="57.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="26"/>
+      <c r="A11" s="27"/>
       <c r="B11" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="25"/>
+        <v>51</v>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="26"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" s="1" customFormat="1" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="26"/>
+      <c r="A12" s="27"/>
       <c r="B12" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="25"/>
+        <v>60</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="26"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -4729,7 +4814,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -4737,145 +4822,145 @@
       <c r="J1" s="8"/>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="26" t="s">
-        <v>68</v>
+      <c r="A2" s="27" t="s">
+        <v>62</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>78</v>
+      <c r="D2" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" ht="87.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="26"/>
+      <c r="A3" s="27"/>
       <c r="B3" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="25"/>
+        <v>95</v>
+      </c>
+      <c r="C3" s="28"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="26"/>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="107.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="26"/>
+      <c r="A4" s="27"/>
       <c r="B4" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="25"/>
+        <v>96</v>
+      </c>
+      <c r="C4" s="28"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="26"/>
     </row>
     <row r="5" spans="1:10" s="1" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="26"/>
+      <c r="A5" s="27"/>
       <c r="B5" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="25"/>
+        <v>43</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="26"/>
     </row>
     <row r="6" spans="1:10" s="1" customFormat="1" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="26"/>
+      <c r="A6" s="27"/>
       <c r="B6" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="25"/>
+        <v>88</v>
+      </c>
+      <c r="C6" s="28"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="26"/>
     </row>
     <row r="7" spans="1:10" s="1" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="26"/>
+      <c r="A7" s="27"/>
       <c r="B7" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="27"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="25"/>
+        <v>77</v>
+      </c>
+      <c r="C7" s="28"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="26"/>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="26"/>
+      <c r="A8" s="27"/>
       <c r="B8" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="25"/>
+        <v>47</v>
+      </c>
+      <c r="C8" s="28"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="26"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="26"/>
+      <c r="A9" s="27"/>
       <c r="B9" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="25"/>
+        <v>48</v>
+      </c>
+      <c r="C9" s="28"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="26"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" s="1" customFormat="1" ht="58.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="26"/>
+      <c r="A10" s="27"/>
       <c r="B10" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="25"/>
+        <v>63</v>
+      </c>
+      <c r="C10" s="28"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="26"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" s="1" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="26"/>
+      <c r="A11" s="27"/>
       <c r="B11" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="25"/>
+        <v>51</v>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="26"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" s="1" customFormat="1" ht="54.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="26"/>
+      <c r="A12" s="27"/>
       <c r="B12" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="25"/>
+        <v>64</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="26"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A13" s="26"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="25"/>
+      <c r="A13" s="27"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E14" s="1"/>
     </row>
@@ -4933,7 +5018,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -4941,99 +5026,99 @@
       <c r="J1" s="8"/>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="29" t="s">
-        <v>103</v>
+      <c r="A2" s="30" t="s">
+        <v>97</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>104</v>
+      <c r="D2" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="32"/>
+      <c r="A3" s="33"/>
       <c r="B3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="28"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="26"/>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="50.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="33"/>
+      <c r="B4" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="28"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="26"/>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="70.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="33"/>
+      <c r="B5" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="25"/>
-    </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="50.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="32"/>
-      <c r="B4" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="25"/>
-    </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" ht="70.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="32"/>
-      <c r="B5" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="25"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="26"/>
     </row>
     <row r="6" spans="1:10" s="1" customFormat="1" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="32"/>
+      <c r="A6" s="33"/>
       <c r="B6" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="28"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="26"/>
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="33"/>
+      <c r="B7" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="28"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="26"/>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="33"/>
+      <c r="B8" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="25"/>
-    </row>
-    <row r="7" spans="1:10" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="32"/>
-      <c r="B7" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="27"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="25"/>
-    </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="32"/>
-      <c r="B8" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="25"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="26"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" s="1" customFormat="1" ht="73.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="32"/>
+      <c r="A9" s="33"/>
       <c r="B9" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="25"/>
+        <v>80</v>
+      </c>
+      <c r="C9" s="28"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="26"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" s="1" customFormat="1" ht="70.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="32"/>
+      <c r="A10" s="33"/>
       <c r="B10" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="25"/>
+        <v>61</v>
+      </c>
+      <c r="C10" s="28"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="26"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -5117,7 +5202,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -5126,153 +5211,153 @@
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="110.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="11" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="26" t="s">
-        <v>92</v>
+      <c r="A3" s="27" t="s">
+        <v>86</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="E3" s="31" t="s">
-        <v>113</v>
+        <v>116</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="91.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="26"/>
+      <c r="A4" s="27"/>
       <c r="B4" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="25"/>
+        <v>99</v>
+      </c>
+      <c r="C4" s="28"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="26"/>
     </row>
     <row r="5" spans="1:10" s="1" customFormat="1" ht="89.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="26"/>
+      <c r="A5" s="27"/>
       <c r="B5" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="25"/>
+        <v>102</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="26"/>
     </row>
     <row r="6" spans="1:10" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="26"/>
+      <c r="A6" s="27"/>
       <c r="B6" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="25"/>
+        <v>43</v>
+      </c>
+      <c r="C6" s="28"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="26"/>
     </row>
     <row r="7" spans="1:10" s="1" customFormat="1" ht="105.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="26"/>
+      <c r="A7" s="27"/>
       <c r="B7" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" s="27"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="25"/>
+        <v>100</v>
+      </c>
+      <c r="C7" s="28"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="26"/>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="124.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="26"/>
+      <c r="A8" s="27"/>
       <c r="B8" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="25"/>
+        <v>101</v>
+      </c>
+      <c r="C8" s="28"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="26"/>
       <c r="H8" s="20"/>
       <c r="I8" s="20"/>
       <c r="J8" s="20"/>
     </row>
     <row r="9" spans="1:10" s="1" customFormat="1" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="26"/>
+      <c r="A9" s="27"/>
       <c r="B9" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="25"/>
+        <v>103</v>
+      </c>
+      <c r="C9" s="28"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="26"/>
       <c r="H9" s="20"/>
       <c r="I9" s="20"/>
       <c r="J9" s="20"/>
     </row>
     <row r="10" spans="1:10" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="26"/>
+      <c r="A10" s="27"/>
       <c r="B10" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="25"/>
+        <v>77</v>
+      </c>
+      <c r="C10" s="28"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="26"/>
       <c r="H10" s="20"/>
       <c r="I10" s="20"/>
       <c r="J10" s="20"/>
     </row>
     <row r="11" spans="1:10" s="1" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="26"/>
+      <c r="A11" s="27"/>
       <c r="B11" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="25"/>
+        <v>47</v>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="26"/>
       <c r="H11" s="20"/>
       <c r="I11" s="20"/>
       <c r="J11" s="20"/>
     </row>
     <row r="12" spans="1:10" s="1" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="26"/>
+      <c r="A12" s="27"/>
       <c r="B12" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="25"/>
+        <v>48</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="26"/>
       <c r="H12" s="20"/>
       <c r="I12" s="20"/>
       <c r="J12" s="20"/>
     </row>
     <row r="13" spans="1:10" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="26"/>
+      <c r="A13" s="27"/>
       <c r="B13" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="25"/>
+        <v>63</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:10" ht="60.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="26"/>
+      <c r="A14" s="27"/>
       <c r="B14" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="25"/>
+        <v>51</v>
+      </c>
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="26"/>
     </row>
     <row r="15" spans="1:10" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="A15" s="26"/>
+      <c r="A15" s="27"/>
       <c r="B15" s="16" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>16</v>
@@ -5282,106 +5367,106 @@
     </row>
     <row r="17" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A18" s="29" t="s">
-        <v>118</v>
+      <c r="A18" s="30" t="s">
+        <v>112</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>119</v>
-      </c>
-      <c r="E18" s="31" t="s">
-        <v>104</v>
+      <c r="D18" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" s="32" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A19" s="32"/>
+      <c r="A19" s="33"/>
       <c r="B19" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="28"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="26"/>
+    </row>
+    <row r="20" spans="1:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A20" s="33"/>
+      <c r="B20" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="28"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="26"/>
+    </row>
+    <row r="21" spans="1:5" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A21" s="33"/>
+      <c r="B21" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="25"/>
-    </row>
-    <row r="20" spans="1:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A20" s="32"/>
-      <c r="B20" s="21" t="s">
+      <c r="C21" s="28"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="26"/>
+    </row>
+    <row r="22" spans="1:5" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="33"/>
+      <c r="B22" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="28"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="26"/>
+    </row>
+    <row r="23" spans="1:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A23" s="33"/>
+      <c r="B23" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="28"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="26"/>
+    </row>
+    <row r="24" spans="1:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A24" s="33"/>
+      <c r="B24" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="28"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="26"/>
+    </row>
+    <row r="25" spans="1:5" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="33"/>
+      <c r="B25" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="25"/>
-    </row>
-    <row r="21" spans="1:5" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="A21" s="32"/>
-      <c r="B21" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" s="27"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="25"/>
-    </row>
-    <row r="22" spans="1:5" ht="53.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="32"/>
-      <c r="B22" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" s="27"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="25"/>
-    </row>
-    <row r="23" spans="1:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A23" s="32"/>
-      <c r="B23" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="25"/>
-    </row>
-    <row r="24" spans="1:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A24" s="32"/>
-      <c r="B24" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" s="27"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="25"/>
-    </row>
-    <row r="25" spans="1:5" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="32"/>
-      <c r="B25" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" s="27"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="25"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="26"/>
     </row>
     <row r="26" spans="1:5" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="A26" s="32"/>
+      <c r="A26" s="33"/>
       <c r="B26" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="27"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="25"/>
+        <v>61</v>
+      </c>
+      <c r="C26" s="28"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -5427,7 +5512,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -5436,61 +5521,61 @@
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="187.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B2" s="33" t="s">
-        <v>126</v>
+        <v>115</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>120</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" ht="159" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="11" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="11" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="1" customFormat="1" ht="172.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="23" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="1" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5579,7 +5664,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -5588,30 +5673,30 @@
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="193.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="B2" s="33" t="s">
-        <v>139</v>
+        <v>129</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>133</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="11" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.4">
